--- a/KoF/2026_KoF_Resutl.xlsx
+++ b/KoF/2026_KoF_Resutl.xlsx
@@ -3,21 +3,21 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C52782-E188-4F8F-BCE5-3405E9C20059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F32CA77-6C49-447A-9715-F9D443BB3384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{521ED91F-5C26-4B0E-8403-9E93154C70E8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{521ED91F-5C26-4B0E-8403-9E93154C70E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Guide" sheetId="9" r:id="rId1"/>
     <sheet name="Totalt" sheetId="8" r:id="rId2"/>
     <sheet name="Resultat" sheetId="1" r:id="rId3"/>
-    <sheet name="Results_of_the_day" sheetId="4" r:id="rId4"/>
+    <sheet name="DayRankSpeed" sheetId="4" r:id="rId4"/>
     <sheet name="Regler" sheetId="2" r:id="rId5"/>
     <sheet name="User ID" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">DayRankSpeed!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Resultat!$A$4:$AZ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Results_of_the_day!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Totalt!$A$3:$AG$4</definedName>
     <definedName name="_Poängställning_01">"$#REF!.$A$302"</definedName>
     <definedName name="_poängställning_rekord">"$#REF!.$A$249"</definedName>
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="109">
   <si>
     <t>Rank</t>
   </si>
@@ -388,12 +388,6 @@
     <t>e.g</t>
   </si>
   <si>
-    <t>https://www.gps-speedsurfing.com/default.aspx?mnu=forum&amp;forum=2&amp;val=230014</t>
-  </si>
-  <si>
-    <t>Got to "Result of  the day"</t>
-  </si>
-  <si>
     <t>Step</t>
   </si>
   <si>
@@ -483,6 +477,12 @@
       </rPr>
       <t>(5x10s)</t>
     </r>
+  </si>
+  <si>
+    <t>Henrik Larsson</t>
+  </si>
+  <si>
+    <t>Got to "Day Rank - speed"</t>
   </si>
 </sst>
 </file>
@@ -1267,19 +1267,37 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="7" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="7" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="7" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="13" fillId="7" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="13" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1292,24 +1310,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="13" fillId="7" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="13" fillId="7" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="13" fillId="7" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="13" fillId="7" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1359,94 +1359,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>4897003</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>135614</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{409E1ED2-C183-22AC-A749-041398A1574B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="571500" y="466725"/>
-          <a:ext cx="8255518" cy="2572109"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>4931277</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>171937</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A17AEA53-16AB-82C4-93CA-D0EBA297342E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="723900" y="3552825"/>
-          <a:ext cx="8141202" cy="3488542"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
       <xdr:row>41</xdr:row>
@@ -1472,7 +1384,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1497,8 +1409,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1369633</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>359983</xdr:colOff>
       <xdr:row>47</xdr:row>
       <xdr:rowOff>135325</xdr:rowOff>
     </xdr:to>
@@ -1516,7 +1428,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1541,8 +1453,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>419622</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>19572</xdr:colOff>
       <xdr:row>82</xdr:row>
       <xdr:rowOff>131920</xdr:rowOff>
     </xdr:to>
@@ -1560,7 +1472,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1585,8 +1497,8 @@
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>4098116</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>250016</xdr:colOff>
       <xdr:row>67</xdr:row>
       <xdr:rowOff>114386</xdr:rowOff>
     </xdr:to>
@@ -1604,7 +1516,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1629,8 +1541,8 @@
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1577965</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>568315</xdr:colOff>
       <xdr:row>93</xdr:row>
       <xdr:rowOff>169767</xdr:rowOff>
     </xdr:to>
@@ -1648,7 +1560,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1673,8 +1585,8 @@
       <xdr:rowOff>102870</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>4750267</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>83017</xdr:colOff>
       <xdr:row>108</xdr:row>
       <xdr:rowOff>55415</xdr:rowOff>
     </xdr:to>
@@ -1692,7 +1604,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1736,7 +1648,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1761,8 +1673,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1714739</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>239</xdr:colOff>
       <xdr:row>119</xdr:row>
       <xdr:rowOff>114468</xdr:rowOff>
     </xdr:to>
@@ -1780,7 +1692,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1789,6 +1701,50 @@
         <a:xfrm>
           <a:off x="609600" y="20450175"/>
           <a:ext cx="1714739" cy="1200318"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>383091</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>152926</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F93C5FAC-2148-F8D3-0514-EC719D81F644}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="3810000"/>
+          <a:ext cx="14984916" cy="3772426"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2122,12 +2078,12 @@
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
     <col min="3" max="3" width="22.7109375" customWidth="1"/>
-    <col min="4" max="4" width="74.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2135,21 +2091,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
         <v>88</v>
       </c>
-      <c r="D2" s="49" t="s">
-        <v>89</v>
-      </c>
+      <c r="D2" s="49"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -2157,7 +2111,7 @@
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -2165,7 +2119,7 @@
         <v>4</v>
       </c>
       <c r="B51" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -2451,7 +2405,7 @@
         <v>5</v>
       </c>
       <c r="B63" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -2459,7 +2413,7 @@
         <v>6</v>
       </c>
       <c r="B85" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -2467,7 +2421,7 @@
         <v>7</v>
       </c>
       <c r="B97" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -2475,15 +2429,12 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{9DAA8712-71B6-46AB-9B58-44B50B167684}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2503,15 +2454,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="17" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B1" s="71" t="s">
-        <v>108</v>
-      </c>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
+      <c r="B1" s="79" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
       <c r="I1" s="24"/>
       <c r="J1" s="16"/>
       <c r="K1" s="24"/>
@@ -2537,120 +2488,120 @@
     <row r="2" spans="1:33" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
-      <c r="D2" s="69">
+      <c r="D2" s="73">
         <v>1</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69">
+      <c r="E2" s="73"/>
+      <c r="F2" s="73">
         <v>2</v>
       </c>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69">
+      <c r="G2" s="73"/>
+      <c r="H2" s="73">
         <v>3</v>
       </c>
-      <c r="I2" s="69"/>
-      <c r="J2" s="80">
+      <c r="I2" s="73"/>
+      <c r="J2" s="74">
         <v>4</v>
       </c>
-      <c r="K2" s="80"/>
-      <c r="L2" s="69">
+      <c r="K2" s="74"/>
+      <c r="L2" s="73">
         <v>5</v>
       </c>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69">
+      <c r="M2" s="73"/>
+      <c r="N2" s="73">
         <v>6</v>
       </c>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69">
+      <c r="O2" s="73"/>
+      <c r="P2" s="73">
         <v>7</v>
       </c>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69">
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73">
         <v>8</v>
       </c>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69">
+      <c r="S2" s="73"/>
+      <c r="T2" s="73">
         <v>9</v>
       </c>
-      <c r="U2" s="69"/>
-      <c r="V2" s="69">
+      <c r="U2" s="73"/>
+      <c r="V2" s="73">
         <v>10</v>
       </c>
-      <c r="W2" s="69"/>
-      <c r="X2" s="69">
+      <c r="W2" s="73"/>
+      <c r="X2" s="73">
         <v>11</v>
       </c>
-      <c r="Y2" s="69"/>
-      <c r="Z2" s="69">
+      <c r="Y2" s="73"/>
+      <c r="Z2" s="73">
         <v>12</v>
       </c>
-      <c r="AA2" s="69"/>
-      <c r="AB2" s="69">
+      <c r="AA2" s="73"/>
+      <c r="AB2" s="73">
         <v>13</v>
       </c>
-      <c r="AC2" s="69"/>
-      <c r="AD2" s="69">
+      <c r="AC2" s="73"/>
+      <c r="AD2" s="73">
         <v>14</v>
       </c>
-      <c r="AE2" s="69"/>
-      <c r="AF2" s="69">
+      <c r="AE2" s="73"/>
+      <c r="AF2" s="73">
         <v>15</v>
       </c>
-      <c r="AG2" s="69"/>
+      <c r="AG2" s="73"/>
     </row>
     <row r="3" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="72" t="s">
+      <c r="A3" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="72" t="s">
+      <c r="C3" s="71" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="74">
+      <c r="D3" s="80">
         <v>45802</v>
       </c>
-      <c r="E3" s="74"/>
-      <c r="F3" s="75">
+      <c r="E3" s="80"/>
+      <c r="F3" s="81">
         <v>45815</v>
       </c>
-      <c r="G3" s="75"/>
-      <c r="H3" s="76">
+      <c r="G3" s="81"/>
+      <c r="H3" s="82">
         <v>45817</v>
       </c>
-      <c r="I3" s="77"/>
-      <c r="J3" s="81">
+      <c r="I3" s="83"/>
+      <c r="J3" s="75">
         <v>45837</v>
       </c>
-      <c r="K3" s="82"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="70"/>
-      <c r="N3" s="70"/>
-      <c r="O3" s="70"/>
-      <c r="P3" s="70"/>
-      <c r="Q3" s="70"/>
-      <c r="R3" s="70"/>
-      <c r="S3" s="70"/>
-      <c r="T3" s="70"/>
-      <c r="U3" s="70"/>
-      <c r="V3" s="70"/>
-      <c r="W3" s="70"/>
-      <c r="X3" s="70"/>
-      <c r="Y3" s="70"/>
-      <c r="Z3" s="70"/>
-      <c r="AA3" s="70"/>
-      <c r="AB3" s="70"/>
-      <c r="AC3" s="70"/>
-      <c r="AD3" s="70"/>
-      <c r="AE3" s="70"/>
-      <c r="AF3" s="70"/>
-      <c r="AG3" s="70"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="78"/>
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="W3" s="78"/>
+      <c r="X3" s="78"/>
+      <c r="Y3" s="78"/>
+      <c r="Z3" s="78"/>
+      <c r="AA3" s="78"/>
+      <c r="AB3" s="78"/>
+      <c r="AC3" s="78"/>
+      <c r="AD3" s="78"/>
+      <c r="AE3" s="78"/>
+      <c r="AF3" s="78"/>
+      <c r="AG3" s="78"/>
     </row>
     <row r="4" spans="1:33" s="20" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A4" s="79"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
       <c r="D4" s="31" t="s">
         <v>86</v>
       </c>
@@ -2748,7 +2699,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C5" s="40">
         <f ca="1">_xlfn.XLOOKUP($B5,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -2760,7 +2711,7 @@
       </c>
       <c r="E5" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B5,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
-        <v>34.75</v>
+        <v>33.869999999999997</v>
       </c>
       <c r="F5" s="28">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B5,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
@@ -2881,7 +2832,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="C6" s="40">
         <f ca="1">_xlfn.XLOOKUP($B6,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -2893,7 +2844,7 @@
       </c>
       <c r="E6" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B6,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
-        <v>31.2</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="F6" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B6,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
@@ -3014,7 +2965,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="C7" s="40">
         <f ca="1">_xlfn.XLOOKUP($B7,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -3026,7 +2977,7 @@
       </c>
       <c r="E7" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B7,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
-        <v>31.1</v>
+        <v>32.44</v>
       </c>
       <c r="F7" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B7,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
@@ -3159,7 +3110,7 @@
       </c>
       <c r="E8" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B8,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
-        <v>31.01</v>
+        <v>31.32</v>
       </c>
       <c r="F8" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B8,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
@@ -3280,7 +3231,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C9" s="40">
         <f ca="1">_xlfn.XLOOKUP($B9,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -3292,7 +3243,7 @@
       </c>
       <c r="E9" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B9,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
-        <v>30.05</v>
+        <v>31.2</v>
       </c>
       <c r="F9" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B9,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
@@ -3413,7 +3364,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C10" s="40">
         <f ca="1">_xlfn.XLOOKUP($B10,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -3425,7 +3376,7 @@
       </c>
       <c r="E10" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B10,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
-        <v>29.71</v>
+        <v>30.96</v>
       </c>
       <c r="F10" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B10,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
@@ -3558,7 +3509,7 @@
       </c>
       <c r="E11" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B11,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
-        <v>29.7</v>
+        <v>30.39</v>
       </c>
       <c r="F11" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B11,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
@@ -3691,7 +3642,7 @@
       </c>
       <c r="E12" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B12,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
-        <v>29.41</v>
+        <v>30.09</v>
       </c>
       <c r="F12" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B12,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
@@ -3812,7 +3763,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="C13" s="40">
         <f ca="1">_xlfn.XLOOKUP($B13,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -3824,7 +3775,7 @@
       </c>
       <c r="E13" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B13,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
-        <v>29.12</v>
+        <v>30.01</v>
       </c>
       <c r="F13" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B13,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
@@ -3957,7 +3908,7 @@
       </c>
       <c r="E14" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B14,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
-        <v>28.9</v>
+        <v>28.02</v>
       </c>
       <c r="F14" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B14,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
@@ -4078,7 +4029,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C15" s="40">
         <f ca="1">_xlfn.XLOOKUP($B15,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -4090,7 +4041,7 @@
       </c>
       <c r="E15" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B15,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
-        <v>28.34</v>
+        <v>27.02</v>
       </c>
       <c r="F15" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B15,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
@@ -4211,7 +4162,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C16" s="40">
         <f ca="1">_xlfn.XLOOKUP($B16,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -4223,7 +4174,7 @@
       </c>
       <c r="E16" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B16,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
-        <v>27.73</v>
+        <v>25.22</v>
       </c>
       <c r="F16" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B16,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
@@ -4344,7 +4295,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="C17" s="40">
         <f ca="1">_xlfn.XLOOKUP($B17,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -4356,7 +4307,7 @@
       </c>
       <c r="E17" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B17,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
-        <v>26.47</v>
+        <v>24.02</v>
       </c>
       <c r="F17" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B17,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
@@ -4477,11 +4428,11 @@
         <v>14</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="C18" s="40">
         <f ca="1">_xlfn.XLOOKUP($B18,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
-        <v>14</v>
+        <v>9999</v>
       </c>
       <c r="D18" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B18,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
@@ -4489,7 +4440,7 @@
       </c>
       <c r="E18" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B18,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
-        <v>25.4</v>
+        <v>0</v>
       </c>
       <c r="F18" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B18,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
@@ -4607,10 +4558,10 @@
     <row r="19" spans="1:33" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="41">
         <f ca="1">_xlfn.XLOOKUP($B19,Resultat!$D:$D,Resultat!$Z:$Z,-1,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="C19" s="40">
         <f ca="1">_xlfn.XLOOKUP($B19,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -4618,7 +4569,7 @@
       </c>
       <c r="D19" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B19,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B19,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
@@ -4740,10 +4691,10 @@
     <row r="20" spans="1:33" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="41">
         <f ca="1">_xlfn.XLOOKUP($B20,Resultat!$D:$D,Resultat!$Z:$Z,-1,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="C20" s="40">
         <f ca="1">_xlfn.XLOOKUP($B20,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -4751,7 +4702,7 @@
       </c>
       <c r="D20" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B20,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E20" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B20,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
@@ -4873,10 +4824,10 @@
     <row r="21" spans="1:33" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="41">
         <f ca="1">_xlfn.XLOOKUP($B21,Resultat!$D:$D,Resultat!$Z:$Z,-1,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="C21" s="40">
         <f ca="1">_xlfn.XLOOKUP($B21,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -4884,7 +4835,7 @@
       </c>
       <c r="D21" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B21,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E21" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B21,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
@@ -5006,10 +4957,10 @@
     <row r="22" spans="1:33" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41">
         <f ca="1">_xlfn.XLOOKUP($B22,Resultat!$D:$D,Resultat!$Z:$Z,-1,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C22" s="40">
         <f ca="1">_xlfn.XLOOKUP($B22,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -5017,7 +4968,7 @@
       </c>
       <c r="D22" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B22,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E22" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B22,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
@@ -5139,10 +5090,10 @@
     <row r="23" spans="1:33" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="41">
         <f ca="1">_xlfn.XLOOKUP($B23,Resultat!$D:$D,Resultat!$Z:$Z,-1,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="C23" s="40">
         <f ca="1">_xlfn.XLOOKUP($B23,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -5150,7 +5101,7 @@
       </c>
       <c r="D23" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B23,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E23" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B23,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
@@ -5272,10 +5223,10 @@
     <row r="24" spans="1:33" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="41">
         <f ca="1">_xlfn.XLOOKUP($B24,Resultat!$D:$D,Resultat!$Z:$Z,-1,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="C24" s="40">
         <f ca="1">_xlfn.XLOOKUP($B24,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -5283,7 +5234,7 @@
       </c>
       <c r="D24" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B24,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E24" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B24,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
@@ -5405,10 +5356,10 @@
     <row r="25" spans="1:33" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="41">
         <f ca="1">_xlfn.XLOOKUP($B25,Resultat!$D:$D,Resultat!$Z:$Z,-1,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C25" s="40">
         <f ca="1">_xlfn.XLOOKUP($B25,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -5416,7 +5367,7 @@
       </c>
       <c r="D25" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B25,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E25" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B25,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
@@ -5538,10 +5489,10 @@
     <row r="26" spans="1:33" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="41">
         <f ca="1">_xlfn.XLOOKUP($B26,Resultat!$D:$D,Resultat!$Z:$Z,-1,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="C26" s="40">
         <f ca="1">_xlfn.XLOOKUP($B26,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -5549,7 +5500,7 @@
       </c>
       <c r="D26" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B26,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E26" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B26,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
@@ -5671,10 +5622,10 @@
     <row r="27" spans="1:33" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="41">
         <f ca="1">_xlfn.XLOOKUP($B27,Resultat!$D:$D,Resultat!$Z:$Z,-1,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C27" s="40">
         <f ca="1">_xlfn.XLOOKUP($B27,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -5682,7 +5633,7 @@
       </c>
       <c r="D27" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B27,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E27" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B27,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
@@ -5804,10 +5755,10 @@
     <row r="28" spans="1:33" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="41">
         <f ca="1">_xlfn.XLOOKUP($B28,Resultat!$D:$D,Resultat!$Z:$Z,-1,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C28" s="40">
         <f ca="1">_xlfn.XLOOKUP($B28,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -5815,7 +5766,7 @@
       </c>
       <c r="D28" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B28,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E28" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B28,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
@@ -5937,10 +5888,10 @@
     <row r="29" spans="1:33" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="41">
         <f ca="1">_xlfn.XLOOKUP($B29,Resultat!$D:$D,Resultat!$Z:$Z,-1,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="C29" s="40">
         <f ca="1">_xlfn.XLOOKUP($B29,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -5948,7 +5899,7 @@
       </c>
       <c r="D29" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B29,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E29" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B29,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
@@ -6070,10 +6021,10 @@
     <row r="30" spans="1:33" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="41">
         <f ca="1">_xlfn.XLOOKUP($B30,Resultat!$D:$D,Resultat!$Z:$Z,-1,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="C30" s="40">
         <f ca="1">_xlfn.XLOOKUP($B30,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
@@ -6081,7 +6032,7 @@
       </c>
       <c r="D30" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B30,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E30" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B30,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
@@ -6203,7 +6154,7 @@
     <row r="31" spans="1:33" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="41">
         <f ca="1">_xlfn.XLOOKUP($B31,Resultat!$D:$D,Resultat!$Z:$Z,-1,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B31" s="21" t="s">
         <v>55</v>
@@ -6214,7 +6165,7 @@
       </c>
       <c r="D31" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B31,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E31" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B31,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
@@ -6336,7 +6287,7 @@
     <row r="32" spans="1:33" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="41">
         <f ca="1">_xlfn.XLOOKUP($B32,Resultat!$D:$D,Resultat!$Z:$Z,-1,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B32" s="21" t="s">
         <v>68</v>
@@ -6347,7 +6298,7 @@
       </c>
       <c r="D32" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B32,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E32" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B32,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
@@ -6469,7 +6420,7 @@
     <row r="33" spans="1:33" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="41">
         <f ca="1">_xlfn.XLOOKUP($B33,Resultat!$D:$D,Resultat!$Z:$Z,-1,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B33" s="21" t="s">
         <v>81</v>
@@ -6480,7 +6431,7 @@
       </c>
       <c r="D33" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B33,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E33" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B33,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
@@ -6602,7 +6553,7 @@
     <row r="34" spans="1:33" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="41">
         <f ca="1">_xlfn.XLOOKUP($B34,Resultat!$D:$D,Resultat!$Z:$Z,-1,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B34" s="21" t="s">
         <v>58</v>
@@ -6613,7 +6564,7 @@
       </c>
       <c r="D34" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B34,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E34" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B34,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
@@ -6735,7 +6686,7 @@
     <row r="35" spans="1:33" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="41">
         <f ca="1">_xlfn.XLOOKUP($B35,Resultat!$D:$D,Resultat!$Z:$Z,-1,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B35" s="21" t="s">
         <v>57</v>
@@ -6746,7 +6697,7 @@
       </c>
       <c r="D35" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B35,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E35" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B35,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
@@ -6868,7 +6819,7 @@
     <row r="36" spans="1:33" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="41">
         <f ca="1">_xlfn.XLOOKUP($B36,Resultat!$D:$D,Resultat!$Z:$Z,-1,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B36" s="21" t="s">
         <v>85</v>
@@ -6879,7 +6830,7 @@
       </c>
       <c r="D36" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B36,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E36" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B36,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,D$2-1)</f>
@@ -7149,25 +7100,6 @@
     <sortCondition ref="B39:B89"/>
   </sortState>
   <mergeCells count="34">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
     <mergeCell ref="AD2:AE2"/>
     <mergeCell ref="AD3:AE3"/>
     <mergeCell ref="AF2:AG2"/>
@@ -7183,6 +7115,25 @@
     <mergeCell ref="X3:Y3"/>
     <mergeCell ref="Z3:AA3"/>
     <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:AG36">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -7201,15 +7152,16 @@
   <dimension ref="A1:BE36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="9.42578125" style="62" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="19" width="10.28515625" customWidth="1"/>
     <col min="20" max="25" width="2.140625" customWidth="1"/>
     <col min="26" max="26" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="28" max="36" width="9.140625" customWidth="1" outlineLevel="1"/>
     <col min="48" max="57" width="8.85546875" customWidth="1" outlineLevel="1"/>
   </cols>
@@ -7222,7 +7174,7 @@
         <v>28</v>
       </c>
       <c r="E1" s="53">
-        <v>45802</v>
+        <v>46137</v>
       </c>
       <c r="F1" s="53"/>
       <c r="G1" s="53"/>
@@ -7392,7 +7344,7 @@
     <row r="3" spans="1:57" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="15">
         <f>SUM(B5:B36)</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="60"/>
       <c r="E3" s="4" t="s">
@@ -7434,7 +7386,7 @@
         <v>69</v>
       </c>
       <c r="B4" s="63" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>15</v>
@@ -7488,7 +7440,7 @@
         <v>15</v>
       </c>
       <c r="Z4" s="66" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AA4" s="64" t="s">
         <v>26</v>
@@ -7574,90 +7526,90 @@
         <v>1</v>
       </c>
       <c r="B5" s="61">
-        <f t="shared" ref="B5:B36" si="2">IF(C5&gt;0,1,0)</f>
-        <v>0</v>
+        <f>IF(C5&gt;0,1,0)</f>
+        <v>1</v>
       </c>
       <c r="C5" s="56">
-        <f t="shared" ref="C5:C36" si="3">SUM($E5:$S5)/$A$2</f>
-        <v>0</v>
+        <f>SUM($E5:$S5)/$A$2</f>
+        <v>32.799999999999997</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>76</v>
       </c>
       <c r="E5" s="67" cm="1">
-        <f t="array" ref="E5">_xlfn.XLOOKUP($D5&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>0</v>
+        <f t="array" ref="E5">_xlfn.XLOOKUP($D5&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>32.799999999999997</v>
       </c>
       <c r="F5" s="67" cm="1">
-        <f t="array" ref="F5">_xlfn.XLOOKUP($D5&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F5">_xlfn.XLOOKUP($D5&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G5" s="67" cm="1">
-        <f t="array" ref="G5">_xlfn.XLOOKUP($D5&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G5">_xlfn.XLOOKUP($D5&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H5" s="67" cm="1">
-        <f t="array" ref="H5">_xlfn.XLOOKUP($D5&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H5">_xlfn.XLOOKUP($D5&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I5" s="67" cm="1">
-        <f t="array" ref="I5">_xlfn.XLOOKUP($D5&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I5">_xlfn.XLOOKUP($D5&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J5" s="67" cm="1">
-        <f t="array" ref="J5">_xlfn.XLOOKUP($D5&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J5">_xlfn.XLOOKUP($D5&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K5" s="67" cm="1">
-        <f t="array" ref="K5">_xlfn.XLOOKUP($D5&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K5">_xlfn.XLOOKUP($D5&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L5" s="67" cm="1">
-        <f t="array" ref="L5">_xlfn.XLOOKUP($D5&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L5">_xlfn.XLOOKUP($D5&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M5" s="67" cm="1">
-        <f t="array" ref="M5">_xlfn.XLOOKUP($D5&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M5">_xlfn.XLOOKUP($D5&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N5" s="67" cm="1">
-        <f t="array" ref="N5">_xlfn.XLOOKUP($D5&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N5">_xlfn.XLOOKUP($D5&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O5" s="67" cm="1">
-        <f t="array" ref="O5">_xlfn.XLOOKUP($D5&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O5">_xlfn.XLOOKUP($D5&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P5" s="67" cm="1">
-        <f t="array" ref="P5">_xlfn.XLOOKUP($D5&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P5">_xlfn.XLOOKUP($D5&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q5" s="67" cm="1">
-        <f t="array" ref="Q5">_xlfn.XLOOKUP($D5&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q5">_xlfn.XLOOKUP($D5&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R5" s="67" cm="1">
-        <f t="array" ref="R5">_xlfn.XLOOKUP($D5&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R5">_xlfn.XLOOKUP($D5&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S5" s="67" cm="1">
-        <f t="array" ref="S5">_xlfn.XLOOKUP($D5&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S5">_xlfn.XLOOKUP($D5&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z5" s="5">
-        <f t="shared" ref="Z5:Z36" ca="1" si="4">_xlfn.RANK.EQ(AA5,$AA$5:$AA$36,1)</f>
-        <v>15</v>
+        <f t="shared" ref="Z5:Z36" ca="1" si="2">_xlfn.RANK.EQ(AA5,$AA$5:$AA$36,1)</f>
+        <v>2</v>
       </c>
       <c r="AA5" s="2">
-        <f t="shared" ref="AA5:AA36" ca="1" si="5">IF($B5,OFFSET(AK5,0,-$B$2),9999)</f>
-        <v>9999</v>
+        <f ca="1">IF($B5,OFFSET(AK5,0,-$B$2),9999)</f>
+        <v>2</v>
       </c>
       <c r="AB5">
-        <f t="shared" ref="AB5:AJ5" si="6">AC5-LARGE($AL5:$AZ5,AB$3)</f>
+        <f t="shared" ref="AB5:AJ5" si="3">AC5-LARGE($AL5:$AZ5,AB$3)</f>
         <v>0</v>
       </c>
       <c r="AC5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD5">
@@ -7669,11 +7621,11 @@
         <v>0</v>
       </c>
       <c r="AF5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH5">
@@ -7681,75 +7633,75 @@
         <v>0</v>
       </c>
       <c r="AI5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK5">
-        <f t="shared" ref="AK5:AK36" si="7">SUM(AL5:AZ5)</f>
-        <v>15</v>
+        <f t="shared" ref="AK5:AK36" si="4">SUM(AL5:AZ5)</f>
+        <v>2</v>
       </c>
       <c r="AL5" s="1">
-        <f t="shared" ref="AL5:AL36" si="8">IF(E5&gt;0,_xlfn.RANK.EQ(E5,E$5:E$36,0),$A$3+1)*AL$2</f>
-        <v>15</v>
+        <f t="shared" ref="AL5:AL36" si="5">IF(E5&gt;0,_xlfn.RANK.EQ(E5,E$5:E$36,0),$A$3+1)*AL$2</f>
+        <v>2</v>
       </c>
       <c r="AM5" s="1">
-        <f t="shared" ref="AM5:AM36" si="9">IF(F5&gt;0,_xlfn.RANK.EQ(F5,F$5:F$36,0),$A$3+1)*AM$2</f>
+        <f t="shared" ref="AM5:AM36" si="6">IF(F5&gt;0,_xlfn.RANK.EQ(F5,F$5:F$36,0),$A$3+1)*AM$2</f>
         <v>0</v>
       </c>
       <c r="AN5" s="1">
-        <f t="shared" ref="AN5:AN36" si="10">IF(G5&gt;0,_xlfn.RANK.EQ(G5,G$5:G$36,0),$A$3+1)*AN$2</f>
+        <f t="shared" ref="AN5:AN36" si="7">IF(G5&gt;0,_xlfn.RANK.EQ(G5,G$5:G$36,0),$A$3+1)*AN$2</f>
         <v>0</v>
       </c>
       <c r="AO5" s="1">
-        <f t="shared" ref="AO5:AO36" si="11">IF(H5&gt;0,_xlfn.RANK.EQ(H5,H$5:H$36,0),$A$3+1)*AO$2</f>
+        <f t="shared" ref="AO5:AO36" si="8">IF(H5&gt;0,_xlfn.RANK.EQ(H5,H$5:H$36,0),$A$3+1)*AO$2</f>
         <v>0</v>
       </c>
       <c r="AP5" s="1">
-        <f t="shared" ref="AP5:AP36" si="12">IF(I5&gt;0,_xlfn.RANK.EQ(I5,I$5:I$36,0),$A$3+1)*AP$2</f>
+        <f t="shared" ref="AP5:AP36" si="9">IF(I5&gt;0,_xlfn.RANK.EQ(I5,I$5:I$36,0),$A$3+1)*AP$2</f>
         <v>0</v>
       </c>
       <c r="AQ5" s="1">
-        <f t="shared" ref="AQ5:AQ36" si="13">IF(J5&gt;0,_xlfn.RANK.EQ(J5,J$5:J$36,0),$A$3+1)*AQ$2</f>
+        <f t="shared" ref="AQ5:AQ36" si="10">IF(J5&gt;0,_xlfn.RANK.EQ(J5,J$5:J$36,0),$A$3+1)*AQ$2</f>
         <v>0</v>
       </c>
       <c r="AR5" s="1">
-        <f t="shared" ref="AR5:AR36" si="14">IF(K5&gt;0,_xlfn.RANK.EQ(K5,K$5:K$36,0),$A$3+1)*AR$2</f>
+        <f t="shared" ref="AR5:AR36" si="11">IF(K5&gt;0,_xlfn.RANK.EQ(K5,K$5:K$36,0),$A$3+1)*AR$2</f>
         <v>0</v>
       </c>
       <c r="AS5" s="1">
-        <f t="shared" ref="AS5:AS36" si="15">IF(L5&gt;0,_xlfn.RANK.EQ(L5,L$5:L$36,0),$A$3+1)*AS$2</f>
+        <f t="shared" ref="AS5:AS36" si="12">IF(L5&gt;0,_xlfn.RANK.EQ(L5,L$5:L$36,0),$A$3+1)*AS$2</f>
         <v>0</v>
       </c>
       <c r="AT5" s="1">
-        <f t="shared" ref="AT5:AT36" si="16">IF(M5&gt;0,_xlfn.RANK.EQ(M5,M$5:M$36,0),$A$3+1)*AT$2</f>
+        <f t="shared" ref="AT5:AT36" si="13">IF(M5&gt;0,_xlfn.RANK.EQ(M5,M$5:M$36,0),$A$3+1)*AT$2</f>
         <v>0</v>
       </c>
       <c r="AU5" s="1">
-        <f t="shared" ref="AU5:AU36" si="17">IF(N5&gt;0,_xlfn.RANK.EQ(N5,N$5:N$36,0),$A$3+1)*AU$2</f>
+        <f t="shared" ref="AU5:AU36" si="14">IF(N5&gt;0,_xlfn.RANK.EQ(N5,N$5:N$36,0),$A$3+1)*AU$2</f>
         <v>0</v>
       </c>
       <c r="AV5" s="1">
-        <f t="shared" ref="AV5:AV36" si="18">IF(O5&gt;0,_xlfn.RANK.EQ(O5,O$5:O$36,0),$A$3+1)*AV$2</f>
+        <f t="shared" ref="AV5:AV36" si="15">IF(O5&gt;0,_xlfn.RANK.EQ(O5,O$5:O$36,0),$A$3+1)*AV$2</f>
         <v>0</v>
       </c>
       <c r="AW5" s="1">
-        <f t="shared" ref="AW5:AW36" si="19">IF(P5&gt;0,_xlfn.RANK.EQ(P5,P$5:P$36,0),$A$3+1)*AW$2</f>
+        <f t="shared" ref="AW5:AW36" si="16">IF(P5&gt;0,_xlfn.RANK.EQ(P5,P$5:P$36,0),$A$3+1)*AW$2</f>
         <v>0</v>
       </c>
       <c r="AX5" s="1">
-        <f t="shared" ref="AX5:AX36" si="20">IF(Q5&gt;0,_xlfn.RANK.EQ(Q5,Q$5:Q$36,0),$A$3+1)*AX$2</f>
+        <f t="shared" ref="AX5:AX36" si="17">IF(Q5&gt;0,_xlfn.RANK.EQ(Q5,Q$5:Q$36,0),$A$3+1)*AX$2</f>
         <v>0</v>
       </c>
       <c r="AY5" s="1">
-        <f t="shared" ref="AY5:AY36" si="21">IF(R5&gt;0,_xlfn.RANK.EQ(R5,R$5:R$36,0),$A$3+1)*AY$2</f>
+        <f t="shared" ref="AY5:AY36" si="18">IF(R5&gt;0,_xlfn.RANK.EQ(R5,R$5:R$36,0),$A$3+1)*AY$2</f>
         <v>0</v>
       </c>
       <c r="AZ5" s="1">
-        <f t="shared" ref="AZ5:AZ36" si="22">IF(S5&gt;0,_xlfn.RANK.EQ(S5,S$5:S$36,0),$A$3+1)*AZ$2</f>
+        <f t="shared" ref="AZ5:AZ36" si="19">IF(S5&gt;0,_xlfn.RANK.EQ(S5,S$5:S$36,0),$A$3+1)*AZ$2</f>
         <v>0</v>
       </c>
     </row>
@@ -7758,82 +7710,82 @@
         <v>2</v>
       </c>
       <c r="B6" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="B5:B36" si="20">IF(C6&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="C6" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="C5:C36" si="21">SUM($E6:$S6)/$A$2</f>
         <v>0</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>53</v>
       </c>
       <c r="E6" s="67" cm="1">
-        <f t="array" ref="E6">_xlfn.XLOOKUP($D6&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="E6">_xlfn.XLOOKUP($D6&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="F6" s="67" cm="1">
-        <f t="array" ref="F6">_xlfn.XLOOKUP($D6&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F6">_xlfn.XLOOKUP($D6&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G6" s="67" cm="1">
-        <f t="array" ref="G6">_xlfn.XLOOKUP($D6&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G6">_xlfn.XLOOKUP($D6&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H6" s="67" cm="1">
-        <f t="array" ref="H6">_xlfn.XLOOKUP($D6&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H6">_xlfn.XLOOKUP($D6&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I6" s="67" cm="1">
-        <f t="array" ref="I6">_xlfn.XLOOKUP($D6&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I6">_xlfn.XLOOKUP($D6&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J6" s="67" cm="1">
-        <f t="array" ref="J6">_xlfn.XLOOKUP($D6&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J6">_xlfn.XLOOKUP($D6&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K6" s="67" cm="1">
-        <f t="array" ref="K6">_xlfn.XLOOKUP($D6&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K6">_xlfn.XLOOKUP($D6&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L6" s="67" cm="1">
-        <f t="array" ref="L6">_xlfn.XLOOKUP($D6&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L6">_xlfn.XLOOKUP($D6&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M6" s="67" cm="1">
-        <f t="array" ref="M6">_xlfn.XLOOKUP($D6&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M6">_xlfn.XLOOKUP($D6&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N6" s="67" cm="1">
-        <f t="array" ref="N6">_xlfn.XLOOKUP($D6&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N6">_xlfn.XLOOKUP($D6&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O6" s="67" cm="1">
-        <f t="array" ref="O6">_xlfn.XLOOKUP($D6&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O6">_xlfn.XLOOKUP($D6&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P6" s="67" cm="1">
-        <f t="array" ref="P6">_xlfn.XLOOKUP($D6&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P6">_xlfn.XLOOKUP($D6&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q6" s="67" cm="1">
-        <f t="array" ref="Q6">_xlfn.XLOOKUP($D6&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q6">_xlfn.XLOOKUP($D6&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R6" s="67" cm="1">
-        <f t="array" ref="R6">_xlfn.XLOOKUP($D6&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R6">_xlfn.XLOOKUP($D6&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S6" s="67" cm="1">
-        <f t="array" ref="S6">_xlfn.XLOOKUP($D6&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S6">_xlfn.XLOOKUP($D6&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z6" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="AA6" s="2">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ref="AA5:AA36" ca="1" si="22">IF($B6,OFFSET(AK6,0,-$B$2),9999)</f>
         <v>9999</v>
       </c>
       <c r="AB6">
@@ -7873,67 +7825,67 @@
         <v>0</v>
       </c>
       <c r="AK6">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL6" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM6" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN6" s="1">
         <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="AL6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="1">
         <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="AM6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN6" s="1">
+      <c r="AQ6" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO6" s="1">
+      <c r="AR6" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP6" s="1">
+      <c r="AS6" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ6" s="1">
+      <c r="AT6" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR6" s="1">
+      <c r="AU6" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS6" s="1">
+      <c r="AV6" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT6" s="1">
+      <c r="AW6" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU6" s="1">
+      <c r="AX6" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV6" s="1">
+      <c r="AY6" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW6" s="1">
+      <c r="AZ6" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX6" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY6" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ6" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -7942,82 +7894,82 @@
         <v>3</v>
       </c>
       <c r="B7" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="C7" s="56">
-        <f t="shared" si="3"/>
-        <v>28.9</v>
+        <f t="shared" si="21"/>
+        <v>28.02</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>41</v>
       </c>
       <c r="E7" s="67" cm="1">
-        <f t="array" ref="E7">_xlfn.XLOOKUP($D7&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>28.9</v>
+        <f t="array" ref="E7">_xlfn.XLOOKUP($D7&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>28.02</v>
       </c>
       <c r="F7" s="67" cm="1">
-        <f t="array" ref="F7">_xlfn.XLOOKUP($D7&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F7">_xlfn.XLOOKUP($D7&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G7" s="67" cm="1">
-        <f t="array" ref="G7">_xlfn.XLOOKUP($D7&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G7">_xlfn.XLOOKUP($D7&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H7" s="67" cm="1">
-        <f t="array" ref="H7">_xlfn.XLOOKUP($D7&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H7">_xlfn.XLOOKUP($D7&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I7" s="67" cm="1">
-        <f t="array" ref="I7">_xlfn.XLOOKUP($D7&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I7">_xlfn.XLOOKUP($D7&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J7" s="67" cm="1">
-        <f t="array" ref="J7">_xlfn.XLOOKUP($D7&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J7">_xlfn.XLOOKUP($D7&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K7" s="67" cm="1">
-        <f t="array" ref="K7">_xlfn.XLOOKUP($D7&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K7">_xlfn.XLOOKUP($D7&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L7" s="67" cm="1">
-        <f t="array" ref="L7">_xlfn.XLOOKUP($D7&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L7">_xlfn.XLOOKUP($D7&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M7" s="67" cm="1">
-        <f t="array" ref="M7">_xlfn.XLOOKUP($D7&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M7">_xlfn.XLOOKUP($D7&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N7" s="67" cm="1">
-        <f t="array" ref="N7">_xlfn.XLOOKUP($D7&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N7">_xlfn.XLOOKUP($D7&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O7" s="67" cm="1">
-        <f t="array" ref="O7">_xlfn.XLOOKUP($D7&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O7">_xlfn.XLOOKUP($D7&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P7" s="67" cm="1">
-        <f t="array" ref="P7">_xlfn.XLOOKUP($D7&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P7">_xlfn.XLOOKUP($D7&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q7" s="67" cm="1">
-        <f t="array" ref="Q7">_xlfn.XLOOKUP($D7&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q7">_xlfn.XLOOKUP($D7&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R7" s="67" cm="1">
-        <f t="array" ref="R7">_xlfn.XLOOKUP($D7&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R7">_xlfn.XLOOKUP($D7&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S7" s="67" cm="1">
-        <f t="array" ref="S7">_xlfn.XLOOKUP($D7&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S7">_xlfn.XLOOKUP($D7&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z7" s="5">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="2"/>
         <v>10</v>
       </c>
       <c r="AA7" s="2">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="22"/>
         <v>10</v>
       </c>
       <c r="AB7">
@@ -8057,67 +8009,67 @@
         <v>0</v>
       </c>
       <c r="AK7">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="AL7" s="1">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="AM7" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN7" s="1">
         <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="AL7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="1">
         <f t="shared" si="8"/>
-        <v>10</v>
-      </c>
-      <c r="AM7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN7" s="1">
+      <c r="AQ7" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO7" s="1">
+      <c r="AR7" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP7" s="1">
+      <c r="AS7" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ7" s="1">
+      <c r="AT7" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR7" s="1">
+      <c r="AU7" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS7" s="1">
+      <c r="AV7" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT7" s="1">
+      <c r="AW7" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU7" s="1">
+      <c r="AX7" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV7" s="1">
+      <c r="AY7" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW7" s="1">
+      <c r="AZ7" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX7" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY7" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ7" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -8126,83 +8078,83 @@
         <v>4</v>
       </c>
       <c r="B8" s="61">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="C8" s="56">
-        <f t="shared" si="3"/>
-        <v>28.34</v>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E8" s="67" cm="1">
-        <f t="array" ref="E8">_xlfn.XLOOKUP($D8&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>28.34</v>
+        <f t="array" ref="E8">_xlfn.XLOOKUP($D8&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>0</v>
       </c>
       <c r="F8" s="67" cm="1">
-        <f t="array" ref="F8">_xlfn.XLOOKUP($D8&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F8">_xlfn.XLOOKUP($D8&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G8" s="67" cm="1">
-        <f t="array" ref="G8">_xlfn.XLOOKUP($D8&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G8">_xlfn.XLOOKUP($D8&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H8" s="67" cm="1">
-        <f t="array" ref="H8">_xlfn.XLOOKUP($D8&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H8">_xlfn.XLOOKUP($D8&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I8" s="67" cm="1">
-        <f t="array" ref="I8">_xlfn.XLOOKUP($D8&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I8">_xlfn.XLOOKUP($D8&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J8" s="67" cm="1">
-        <f t="array" ref="J8">_xlfn.XLOOKUP($D8&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J8">_xlfn.XLOOKUP($D8&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K8" s="67" cm="1">
-        <f t="array" ref="K8">_xlfn.XLOOKUP($D8&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K8">_xlfn.XLOOKUP($D8&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L8" s="67" cm="1">
-        <f t="array" ref="L8">_xlfn.XLOOKUP($D8&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L8">_xlfn.XLOOKUP($D8&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M8" s="67" cm="1">
-        <f t="array" ref="M8">_xlfn.XLOOKUP($D8&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M8">_xlfn.XLOOKUP($D8&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N8" s="67" cm="1">
-        <f t="array" ref="N8">_xlfn.XLOOKUP($D8&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N8">_xlfn.XLOOKUP($D8&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O8" s="67" cm="1">
-        <f t="array" ref="O8">_xlfn.XLOOKUP($D8&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O8">_xlfn.XLOOKUP($D8&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P8" s="67" cm="1">
-        <f t="array" ref="P8">_xlfn.XLOOKUP($D8&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P8">_xlfn.XLOOKUP($D8&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q8" s="67" cm="1">
-        <f t="array" ref="Q8">_xlfn.XLOOKUP($D8&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q8">_xlfn.XLOOKUP($D8&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R8" s="67" cm="1">
-        <f t="array" ref="R8">_xlfn.XLOOKUP($D8&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R8">_xlfn.XLOOKUP($D8&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S8" s="67" cm="1">
-        <f t="array" ref="S8">_xlfn.XLOOKUP($D8&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S8">_xlfn.XLOOKUP($D8&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z8" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>11</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="AA8" s="2">
-        <f t="shared" ca="1" si="5"/>
-        <v>11</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>9999</v>
       </c>
       <c r="AB8">
         <f t="shared" si="23"/>
@@ -8241,67 +8193,67 @@
         <v>0</v>
       </c>
       <c r="AK8">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL8" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM8" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN8" s="1">
         <f t="shared" si="7"/>
-        <v>11</v>
-      </c>
-      <c r="AL8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="1">
         <f t="shared" si="8"/>
-        <v>11</v>
-      </c>
-      <c r="AM8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN8" s="1">
+      <c r="AQ8" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO8" s="1">
+      <c r="AR8" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP8" s="1">
+      <c r="AS8" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ8" s="1">
+      <c r="AT8" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR8" s="1">
+      <c r="AU8" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS8" s="1">
+      <c r="AV8" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT8" s="1">
+      <c r="AW8" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU8" s="1">
+      <c r="AX8" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV8" s="1">
+      <c r="AY8" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW8" s="1">
+      <c r="AZ8" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX8" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY8" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ8" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -8310,83 +8262,83 @@
         <v>5</v>
       </c>
       <c r="B9" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="C9" s="56">
-        <f t="shared" si="3"/>
-        <v>26.47</v>
+        <f t="shared" si="21"/>
+        <v>27.02</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>42</v>
       </c>
       <c r="E9" s="67" cm="1">
-        <f t="array" ref="E9">_xlfn.XLOOKUP($D9&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>26.47</v>
+        <f t="array" ref="E9">_xlfn.XLOOKUP($D9&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>27.02</v>
       </c>
       <c r="F9" s="67" cm="1">
-        <f t="array" ref="F9">_xlfn.XLOOKUP($D9&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F9">_xlfn.XLOOKUP($D9&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G9" s="67" cm="1">
-        <f t="array" ref="G9">_xlfn.XLOOKUP($D9&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G9">_xlfn.XLOOKUP($D9&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H9" s="67" cm="1">
-        <f t="array" ref="H9">_xlfn.XLOOKUP($D9&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H9">_xlfn.XLOOKUP($D9&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I9" s="67" cm="1">
-        <f t="array" ref="I9">_xlfn.XLOOKUP($D9&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I9">_xlfn.XLOOKUP($D9&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J9" s="67" cm="1">
-        <f t="array" ref="J9">_xlfn.XLOOKUP($D9&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J9">_xlfn.XLOOKUP($D9&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K9" s="67" cm="1">
-        <f t="array" ref="K9">_xlfn.XLOOKUP($D9&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K9">_xlfn.XLOOKUP($D9&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L9" s="67" cm="1">
-        <f t="array" ref="L9">_xlfn.XLOOKUP($D9&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L9">_xlfn.XLOOKUP($D9&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M9" s="67" cm="1">
-        <f t="array" ref="M9">_xlfn.XLOOKUP($D9&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M9">_xlfn.XLOOKUP($D9&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N9" s="67" cm="1">
-        <f t="array" ref="N9">_xlfn.XLOOKUP($D9&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N9">_xlfn.XLOOKUP($D9&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O9" s="67" cm="1">
-        <f t="array" ref="O9">_xlfn.XLOOKUP($D9&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O9">_xlfn.XLOOKUP($D9&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P9" s="67" cm="1">
-        <f t="array" ref="P9">_xlfn.XLOOKUP($D9&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P9">_xlfn.XLOOKUP($D9&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q9" s="67" cm="1">
-        <f t="array" ref="Q9">_xlfn.XLOOKUP($D9&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q9">_xlfn.XLOOKUP($D9&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R9" s="67" cm="1">
-        <f t="array" ref="R9">_xlfn.XLOOKUP($D9&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R9">_xlfn.XLOOKUP($D9&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S9" s="67" cm="1">
-        <f t="array" ref="S9">_xlfn.XLOOKUP($D9&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S9">_xlfn.XLOOKUP($D9&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z9" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>13</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>11</v>
       </c>
       <c r="AA9" s="2">
-        <f t="shared" ca="1" si="5"/>
-        <v>13</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>11</v>
       </c>
       <c r="AB9">
         <f t="shared" si="23"/>
@@ -8425,67 +8377,67 @@
         <v>0</v>
       </c>
       <c r="AK9">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="AL9" s="1">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="AM9" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN9" s="1">
         <f t="shared" si="7"/>
-        <v>13</v>
-      </c>
-      <c r="AL9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="1">
         <f t="shared" si="8"/>
-        <v>13</v>
-      </c>
-      <c r="AM9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN9" s="1">
+      <c r="AQ9" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO9" s="1">
+      <c r="AR9" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP9" s="1">
+      <c r="AS9" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ9" s="1">
+      <c r="AT9" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR9" s="1">
+      <c r="AU9" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS9" s="1">
+      <c r="AV9" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT9" s="1">
+      <c r="AW9" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU9" s="1">
+      <c r="AX9" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV9" s="1">
+      <c r="AY9" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW9" s="1">
+      <c r="AZ9" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX9" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY9" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ9" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -8494,82 +8446,82 @@
         <v>6</v>
       </c>
       <c r="B10" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="C10" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>81</v>
       </c>
       <c r="E10" s="67" cm="1">
-        <f t="array" ref="E10">_xlfn.XLOOKUP($D10&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="E10">_xlfn.XLOOKUP($D10&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="F10" s="67" cm="1">
-        <f t="array" ref="F10">_xlfn.XLOOKUP($D10&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F10">_xlfn.XLOOKUP($D10&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G10" s="67" cm="1">
-        <f t="array" ref="G10">_xlfn.XLOOKUP($D10&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G10">_xlfn.XLOOKUP($D10&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H10" s="67" cm="1">
-        <f t="array" ref="H10">_xlfn.XLOOKUP($D10&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H10">_xlfn.XLOOKUP($D10&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I10" s="67" cm="1">
-        <f t="array" ref="I10">_xlfn.XLOOKUP($D10&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I10">_xlfn.XLOOKUP($D10&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J10" s="67" cm="1">
-        <f t="array" ref="J10">_xlfn.XLOOKUP($D10&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J10">_xlfn.XLOOKUP($D10&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K10" s="67" cm="1">
-        <f t="array" ref="K10">_xlfn.XLOOKUP($D10&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K10">_xlfn.XLOOKUP($D10&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L10" s="67" cm="1">
-        <f t="array" ref="L10">_xlfn.XLOOKUP($D10&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L10">_xlfn.XLOOKUP($D10&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M10" s="67" cm="1">
-        <f t="array" ref="M10">_xlfn.XLOOKUP($D10&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M10">_xlfn.XLOOKUP($D10&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N10" s="67" cm="1">
-        <f t="array" ref="N10">_xlfn.XLOOKUP($D10&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N10">_xlfn.XLOOKUP($D10&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O10" s="67" cm="1">
-        <f t="array" ref="O10">_xlfn.XLOOKUP($D10&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O10">_xlfn.XLOOKUP($D10&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P10" s="67" cm="1">
-        <f t="array" ref="P10">_xlfn.XLOOKUP($D10&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P10">_xlfn.XLOOKUP($D10&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q10" s="67" cm="1">
-        <f t="array" ref="Q10">_xlfn.XLOOKUP($D10&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q10">_xlfn.XLOOKUP($D10&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R10" s="67" cm="1">
-        <f t="array" ref="R10">_xlfn.XLOOKUP($D10&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R10">_xlfn.XLOOKUP($D10&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S10" s="67" cm="1">
-        <f t="array" ref="S10">_xlfn.XLOOKUP($D10&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S10">_xlfn.XLOOKUP($D10&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z10" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="AA10" s="2">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="22"/>
         <v>9999</v>
       </c>
       <c r="AB10">
@@ -8609,67 +8561,67 @@
         <v>0</v>
       </c>
       <c r="AK10">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL10" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM10" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN10" s="1">
         <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="AL10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="1">
         <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="AM10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN10" s="1">
+      <c r="AQ10" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO10" s="1">
+      <c r="AR10" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP10" s="1">
+      <c r="AS10" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ10" s="1">
+      <c r="AT10" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR10" s="1">
+      <c r="AU10" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS10" s="1">
+      <c r="AV10" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT10" s="1">
+      <c r="AW10" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU10" s="1">
+      <c r="AX10" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV10" s="1">
+      <c r="AY10" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW10" s="1">
+      <c r="AZ10" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX10" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY10" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ10" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -8678,82 +8630,82 @@
         <v>7</v>
       </c>
       <c r="B11" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="C11" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>58</v>
       </c>
       <c r="E11" s="67" cm="1">
-        <f t="array" ref="E11">_xlfn.XLOOKUP($D11&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="E11">_xlfn.XLOOKUP($D11&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="F11" s="67" cm="1">
-        <f t="array" ref="F11">_xlfn.XLOOKUP($D11&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F11">_xlfn.XLOOKUP($D11&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G11" s="67" cm="1">
-        <f t="array" ref="G11">_xlfn.XLOOKUP($D11&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G11">_xlfn.XLOOKUP($D11&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H11" s="67" cm="1">
-        <f t="array" ref="H11">_xlfn.XLOOKUP($D11&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H11">_xlfn.XLOOKUP($D11&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I11" s="67" cm="1">
-        <f t="array" ref="I11">_xlfn.XLOOKUP($D11&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I11">_xlfn.XLOOKUP($D11&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J11" s="67" cm="1">
-        <f t="array" ref="J11">_xlfn.XLOOKUP($D11&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J11">_xlfn.XLOOKUP($D11&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K11" s="67" cm="1">
-        <f t="array" ref="K11">_xlfn.XLOOKUP($D11&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K11">_xlfn.XLOOKUP($D11&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L11" s="67" cm="1">
-        <f t="array" ref="L11">_xlfn.XLOOKUP($D11&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L11">_xlfn.XLOOKUP($D11&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M11" s="67" cm="1">
-        <f t="array" ref="M11">_xlfn.XLOOKUP($D11&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M11">_xlfn.XLOOKUP($D11&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N11" s="67" cm="1">
-        <f t="array" ref="N11">_xlfn.XLOOKUP($D11&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N11">_xlfn.XLOOKUP($D11&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O11" s="67" cm="1">
-        <f t="array" ref="O11">_xlfn.XLOOKUP($D11&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O11">_xlfn.XLOOKUP($D11&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P11" s="67" cm="1">
-        <f t="array" ref="P11">_xlfn.XLOOKUP($D11&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P11">_xlfn.XLOOKUP($D11&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q11" s="67" cm="1">
-        <f t="array" ref="Q11">_xlfn.XLOOKUP($D11&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q11">_xlfn.XLOOKUP($D11&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R11" s="67" cm="1">
-        <f t="array" ref="R11">_xlfn.XLOOKUP($D11&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R11">_xlfn.XLOOKUP($D11&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S11" s="67" cm="1">
-        <f t="array" ref="S11">_xlfn.XLOOKUP($D11&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S11">_xlfn.XLOOKUP($D11&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z11" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="AA11" s="2">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="22"/>
         <v>9999</v>
       </c>
       <c r="AB11">
@@ -8793,67 +8745,67 @@
         <v>0</v>
       </c>
       <c r="AK11">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL11" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM11" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN11" s="1">
         <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="AL11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="1">
         <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="AM11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN11" s="1">
+      <c r="AQ11" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO11" s="1">
+      <c r="AR11" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP11" s="1">
+      <c r="AS11" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ11" s="1">
+      <c r="AT11" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR11" s="1">
+      <c r="AU11" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS11" s="1">
+      <c r="AV11" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT11" s="1">
+      <c r="AW11" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU11" s="1">
+      <c r="AX11" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV11" s="1">
+      <c r="AY11" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW11" s="1">
+      <c r="AZ11" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX11" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY11" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ11" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -8862,82 +8814,82 @@
         <v>8</v>
       </c>
       <c r="B12" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="C12" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>77</v>
       </c>
       <c r="E12" s="67" cm="1">
-        <f t="array" ref="E12">_xlfn.XLOOKUP($D12&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="E12">_xlfn.XLOOKUP($D12&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="F12" s="67" cm="1">
-        <f t="array" ref="F12">_xlfn.XLOOKUP($D12&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F12">_xlfn.XLOOKUP($D12&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G12" s="67" cm="1">
-        <f t="array" ref="G12">_xlfn.XLOOKUP($D12&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G12">_xlfn.XLOOKUP($D12&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H12" s="67" cm="1">
-        <f t="array" ref="H12">_xlfn.XLOOKUP($D12&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H12">_xlfn.XLOOKUP($D12&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I12" s="67" cm="1">
-        <f t="array" ref="I12">_xlfn.XLOOKUP($D12&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I12">_xlfn.XLOOKUP($D12&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J12" s="67" cm="1">
-        <f t="array" ref="J12">_xlfn.XLOOKUP($D12&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J12">_xlfn.XLOOKUP($D12&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K12" s="67" cm="1">
-        <f t="array" ref="K12">_xlfn.XLOOKUP($D12&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K12">_xlfn.XLOOKUP($D12&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L12" s="67" cm="1">
-        <f t="array" ref="L12">_xlfn.XLOOKUP($D12&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L12">_xlfn.XLOOKUP($D12&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M12" s="67" cm="1">
-        <f t="array" ref="M12">_xlfn.XLOOKUP($D12&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M12">_xlfn.XLOOKUP($D12&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N12" s="67" cm="1">
-        <f t="array" ref="N12">_xlfn.XLOOKUP($D12&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N12">_xlfn.XLOOKUP($D12&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O12" s="67" cm="1">
-        <f t="array" ref="O12">_xlfn.XLOOKUP($D12&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O12">_xlfn.XLOOKUP($D12&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P12" s="67" cm="1">
-        <f t="array" ref="P12">_xlfn.XLOOKUP($D12&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P12">_xlfn.XLOOKUP($D12&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q12" s="67" cm="1">
-        <f t="array" ref="Q12">_xlfn.XLOOKUP($D12&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q12">_xlfn.XLOOKUP($D12&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R12" s="67" cm="1">
-        <f t="array" ref="R12">_xlfn.XLOOKUP($D12&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R12">_xlfn.XLOOKUP($D12&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S12" s="67" cm="1">
-        <f t="array" ref="S12">_xlfn.XLOOKUP($D12&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S12">_xlfn.XLOOKUP($D12&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z12" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="AA12" s="2">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="22"/>
         <v>9999</v>
       </c>
       <c r="AB12">
@@ -8977,67 +8929,67 @@
         <v>0</v>
       </c>
       <c r="AK12">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL12" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM12" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN12" s="1">
         <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="AL12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="1">
         <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="AM12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN12" s="1">
+      <c r="AQ12" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO12" s="1">
+      <c r="AR12" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP12" s="1">
+      <c r="AS12" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ12" s="1">
+      <c r="AT12" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR12" s="1">
+      <c r="AU12" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS12" s="1">
+      <c r="AV12" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT12" s="1">
+      <c r="AW12" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU12" s="1">
+      <c r="AX12" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV12" s="1">
+      <c r="AY12" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW12" s="1">
+      <c r="AZ12" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX12" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY12" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ12" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -9046,82 +8998,82 @@
         <v>9</v>
       </c>
       <c r="B13" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="C13" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>55</v>
       </c>
       <c r="E13" s="67" cm="1">
-        <f t="array" ref="E13">_xlfn.XLOOKUP($D13&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="E13">_xlfn.XLOOKUP($D13&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="F13" s="67" cm="1">
-        <f t="array" ref="F13">_xlfn.XLOOKUP($D13&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F13">_xlfn.XLOOKUP($D13&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G13" s="67" cm="1">
-        <f t="array" ref="G13">_xlfn.XLOOKUP($D13&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G13">_xlfn.XLOOKUP($D13&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H13" s="67" cm="1">
-        <f t="array" ref="H13">_xlfn.XLOOKUP($D13&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H13">_xlfn.XLOOKUP($D13&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I13" s="67" cm="1">
-        <f t="array" ref="I13">_xlfn.XLOOKUP($D13&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I13">_xlfn.XLOOKUP($D13&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J13" s="67" cm="1">
-        <f t="array" ref="J13">_xlfn.XLOOKUP($D13&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J13">_xlfn.XLOOKUP($D13&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K13" s="67" cm="1">
-        <f t="array" ref="K13">_xlfn.XLOOKUP($D13&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K13">_xlfn.XLOOKUP($D13&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L13" s="67" cm="1">
-        <f t="array" ref="L13">_xlfn.XLOOKUP($D13&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L13">_xlfn.XLOOKUP($D13&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M13" s="67" cm="1">
-        <f t="array" ref="M13">_xlfn.XLOOKUP($D13&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M13">_xlfn.XLOOKUP($D13&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N13" s="67" cm="1">
-        <f t="array" ref="N13">_xlfn.XLOOKUP($D13&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N13">_xlfn.XLOOKUP($D13&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O13" s="67" cm="1">
-        <f t="array" ref="O13">_xlfn.XLOOKUP($D13&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O13">_xlfn.XLOOKUP($D13&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P13" s="67" cm="1">
-        <f t="array" ref="P13">_xlfn.XLOOKUP($D13&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P13">_xlfn.XLOOKUP($D13&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q13" s="67" cm="1">
-        <f t="array" ref="Q13">_xlfn.XLOOKUP($D13&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q13">_xlfn.XLOOKUP($D13&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R13" s="67" cm="1">
-        <f t="array" ref="R13">_xlfn.XLOOKUP($D13&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R13">_xlfn.XLOOKUP($D13&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S13" s="67" cm="1">
-        <f t="array" ref="S13">_xlfn.XLOOKUP($D13&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S13">_xlfn.XLOOKUP($D13&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z13" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="AA13" s="2">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="22"/>
         <v>9999</v>
       </c>
       <c r="AB13">
@@ -9161,67 +9113,67 @@
         <v>0</v>
       </c>
       <c r="AK13">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL13" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM13" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN13" s="1">
         <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="AL13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="1">
         <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="AM13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN13" s="1">
+      <c r="AQ13" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO13" s="1">
+      <c r="AR13" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP13" s="1">
+      <c r="AS13" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ13" s="1">
+      <c r="AT13" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR13" s="1">
+      <c r="AU13" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS13" s="1">
+      <c r="AV13" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT13" s="1">
+      <c r="AW13" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU13" s="1">
+      <c r="AX13" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV13" s="1">
+      <c r="AY13" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW13" s="1">
+      <c r="AZ13" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX13" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY13" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ13" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -9230,83 +9182,83 @@
         <v>10</v>
       </c>
       <c r="B14" s="61">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="C14" s="56">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>33.869999999999997</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>46</v>
       </c>
       <c r="E14" s="67" cm="1">
-        <f t="array" ref="E14">_xlfn.XLOOKUP($D14&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>0</v>
+        <f t="array" ref="E14">_xlfn.XLOOKUP($D14&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>33.869999999999997</v>
       </c>
       <c r="F14" s="67" cm="1">
-        <f t="array" ref="F14">_xlfn.XLOOKUP($D14&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F14">_xlfn.XLOOKUP($D14&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G14" s="67" cm="1">
-        <f t="array" ref="G14">_xlfn.XLOOKUP($D14&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G14">_xlfn.XLOOKUP($D14&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H14" s="67" cm="1">
-        <f t="array" ref="H14">_xlfn.XLOOKUP($D14&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H14">_xlfn.XLOOKUP($D14&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I14" s="67" cm="1">
-        <f t="array" ref="I14">_xlfn.XLOOKUP($D14&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I14">_xlfn.XLOOKUP($D14&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J14" s="67" cm="1">
-        <f t="array" ref="J14">_xlfn.XLOOKUP($D14&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J14">_xlfn.XLOOKUP($D14&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K14" s="67" cm="1">
-        <f t="array" ref="K14">_xlfn.XLOOKUP($D14&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K14">_xlfn.XLOOKUP($D14&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L14" s="67" cm="1">
-        <f t="array" ref="L14">_xlfn.XLOOKUP($D14&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L14">_xlfn.XLOOKUP($D14&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M14" s="67" cm="1">
-        <f t="array" ref="M14">_xlfn.XLOOKUP($D14&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M14">_xlfn.XLOOKUP($D14&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N14" s="67" cm="1">
-        <f t="array" ref="N14">_xlfn.XLOOKUP($D14&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N14">_xlfn.XLOOKUP($D14&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O14" s="67" cm="1">
-        <f t="array" ref="O14">_xlfn.XLOOKUP($D14&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O14">_xlfn.XLOOKUP($D14&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P14" s="67" cm="1">
-        <f t="array" ref="P14">_xlfn.XLOOKUP($D14&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P14">_xlfn.XLOOKUP($D14&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q14" s="67" cm="1">
-        <f t="array" ref="Q14">_xlfn.XLOOKUP($D14&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q14">_xlfn.XLOOKUP($D14&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R14" s="67" cm="1">
-        <f t="array" ref="R14">_xlfn.XLOOKUP($D14&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R14">_xlfn.XLOOKUP($D14&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S14" s="67" cm="1">
-        <f t="array" ref="S14">_xlfn.XLOOKUP($D14&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S14">_xlfn.XLOOKUP($D14&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z14" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="AA14" s="2">
-        <f t="shared" ca="1" si="5"/>
-        <v>9999</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>1</v>
       </c>
       <c r="AB14">
         <f t="shared" si="23"/>
@@ -9345,67 +9297,67 @@
         <v>0</v>
       </c>
       <c r="AK14">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AL14" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="AM14" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN14" s="1">
         <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="AL14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="1">
         <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="AM14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN14" s="1">
+      <c r="AQ14" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO14" s="1">
+      <c r="AR14" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP14" s="1">
+      <c r="AS14" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ14" s="1">
+      <c r="AT14" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR14" s="1">
+      <c r="AU14" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS14" s="1">
+      <c r="AV14" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT14" s="1">
+      <c r="AW14" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU14" s="1">
+      <c r="AX14" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV14" s="1">
+      <c r="AY14" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW14" s="1">
+      <c r="AZ14" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX14" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY14" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ14" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -9414,83 +9366,83 @@
         <v>11</v>
       </c>
       <c r="B15" s="61">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="C15" s="56">
-        <f t="shared" si="3"/>
-        <v>29.12</v>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>80</v>
       </c>
       <c r="E15" s="67" cm="1">
-        <f t="array" ref="E15">_xlfn.XLOOKUP($D15&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>29.12</v>
+        <f t="array" ref="E15">_xlfn.XLOOKUP($D15&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>0</v>
       </c>
       <c r="F15" s="67" cm="1">
-        <f t="array" ref="F15">_xlfn.XLOOKUP($D15&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F15">_xlfn.XLOOKUP($D15&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G15" s="67" cm="1">
-        <f t="array" ref="G15">_xlfn.XLOOKUP($D15&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G15">_xlfn.XLOOKUP($D15&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H15" s="67" cm="1">
-        <f t="array" ref="H15">_xlfn.XLOOKUP($D15&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H15">_xlfn.XLOOKUP($D15&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I15" s="67" cm="1">
-        <f t="array" ref="I15">_xlfn.XLOOKUP($D15&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I15">_xlfn.XLOOKUP($D15&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J15" s="67" cm="1">
-        <f t="array" ref="J15">_xlfn.XLOOKUP($D15&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J15">_xlfn.XLOOKUP($D15&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K15" s="67" cm="1">
-        <f t="array" ref="K15">_xlfn.XLOOKUP($D15&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K15">_xlfn.XLOOKUP($D15&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L15" s="67" cm="1">
-        <f t="array" ref="L15">_xlfn.XLOOKUP($D15&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L15">_xlfn.XLOOKUP($D15&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M15" s="67" cm="1">
-        <f t="array" ref="M15">_xlfn.XLOOKUP($D15&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M15">_xlfn.XLOOKUP($D15&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N15" s="67" cm="1">
-        <f t="array" ref="N15">_xlfn.XLOOKUP($D15&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N15">_xlfn.XLOOKUP($D15&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O15" s="67" cm="1">
-        <f t="array" ref="O15">_xlfn.XLOOKUP($D15&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O15">_xlfn.XLOOKUP($D15&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P15" s="67" cm="1">
-        <f t="array" ref="P15">_xlfn.XLOOKUP($D15&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P15">_xlfn.XLOOKUP($D15&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q15" s="67" cm="1">
-        <f t="array" ref="Q15">_xlfn.XLOOKUP($D15&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q15">_xlfn.XLOOKUP($D15&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R15" s="67" cm="1">
-        <f t="array" ref="R15">_xlfn.XLOOKUP($D15&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R15">_xlfn.XLOOKUP($D15&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S15" s="67" cm="1">
-        <f t="array" ref="S15">_xlfn.XLOOKUP($D15&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S15">_xlfn.XLOOKUP($D15&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z15" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>9</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="AA15" s="2">
-        <f t="shared" ca="1" si="5"/>
-        <v>9</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>9999</v>
       </c>
       <c r="AB15">
         <f t="shared" si="23"/>
@@ -9529,67 +9481,67 @@
         <v>0</v>
       </c>
       <c r="AK15">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL15" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM15" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN15" s="1">
         <f t="shared" si="7"/>
-        <v>9</v>
-      </c>
-      <c r="AL15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="1">
         <f t="shared" si="8"/>
-        <v>9</v>
-      </c>
-      <c r="AM15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN15" s="1">
+      <c r="AQ15" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO15" s="1">
+      <c r="AR15" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP15" s="1">
+      <c r="AS15" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ15" s="1">
+      <c r="AT15" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR15" s="1">
+      <c r="AU15" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS15" s="1">
+      <c r="AV15" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT15" s="1">
+      <c r="AW15" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU15" s="1">
+      <c r="AX15" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV15" s="1">
+      <c r="AY15" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW15" s="1">
+      <c r="AZ15" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX15" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY15" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ15" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -9598,82 +9550,82 @@
         <v>12</v>
       </c>
       <c r="B16" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="C16" s="56">
-        <f t="shared" si="3"/>
-        <v>29.7</v>
+        <f t="shared" si="21"/>
+        <v>30.39</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>40</v>
       </c>
       <c r="E16" s="67" cm="1">
-        <f t="array" ref="E16">_xlfn.XLOOKUP($D16&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>29.7</v>
+        <f t="array" ref="E16">_xlfn.XLOOKUP($D16&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>30.39</v>
       </c>
       <c r="F16" s="67" cm="1">
-        <f t="array" ref="F16">_xlfn.XLOOKUP($D16&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F16">_xlfn.XLOOKUP($D16&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G16" s="67" cm="1">
-        <f t="array" ref="G16">_xlfn.XLOOKUP($D16&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G16">_xlfn.XLOOKUP($D16&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H16" s="67" cm="1">
-        <f t="array" ref="H16">_xlfn.XLOOKUP($D16&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H16">_xlfn.XLOOKUP($D16&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I16" s="67" cm="1">
-        <f t="array" ref="I16">_xlfn.XLOOKUP($D16&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I16">_xlfn.XLOOKUP($D16&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J16" s="67" cm="1">
-        <f t="array" ref="J16">_xlfn.XLOOKUP($D16&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J16">_xlfn.XLOOKUP($D16&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K16" s="67" cm="1">
-        <f t="array" ref="K16">_xlfn.XLOOKUP($D16&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K16">_xlfn.XLOOKUP($D16&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L16" s="67" cm="1">
-        <f t="array" ref="L16">_xlfn.XLOOKUP($D16&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L16">_xlfn.XLOOKUP($D16&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M16" s="67" cm="1">
-        <f t="array" ref="M16">_xlfn.XLOOKUP($D16&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M16">_xlfn.XLOOKUP($D16&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N16" s="67" cm="1">
-        <f t="array" ref="N16">_xlfn.XLOOKUP($D16&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N16">_xlfn.XLOOKUP($D16&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O16" s="67" cm="1">
-        <f t="array" ref="O16">_xlfn.XLOOKUP($D16&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O16">_xlfn.XLOOKUP($D16&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P16" s="67" cm="1">
-        <f t="array" ref="P16">_xlfn.XLOOKUP($D16&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P16">_xlfn.XLOOKUP($D16&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q16" s="67" cm="1">
-        <f t="array" ref="Q16">_xlfn.XLOOKUP($D16&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q16">_xlfn.XLOOKUP($D16&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R16" s="67" cm="1">
-        <f t="array" ref="R16">_xlfn.XLOOKUP($D16&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R16">_xlfn.XLOOKUP($D16&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S16" s="67" cm="1">
-        <f t="array" ref="S16">_xlfn.XLOOKUP($D16&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S16">_xlfn.XLOOKUP($D16&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z16" s="5">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="2"/>
         <v>7</v>
       </c>
       <c r="AA16" s="2">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="22"/>
         <v>7</v>
       </c>
       <c r="AB16">
@@ -9713,67 +9665,67 @@
         <v>0</v>
       </c>
       <c r="AK16">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="AL16" s="1">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="AM16" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN16" s="1">
         <f t="shared" si="7"/>
-        <v>7</v>
-      </c>
-      <c r="AL16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="1">
         <f t="shared" si="8"/>
-        <v>7</v>
-      </c>
-      <c r="AM16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN16" s="1">
+      <c r="AQ16" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO16" s="1">
+      <c r="AR16" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP16" s="1">
+      <c r="AS16" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ16" s="1">
+      <c r="AT16" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR16" s="1">
+      <c r="AU16" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS16" s="1">
+      <c r="AV16" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT16" s="1">
+      <c r="AW16" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU16" s="1">
+      <c r="AX16" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV16" s="1">
+      <c r="AY16" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW16" s="1">
+      <c r="AZ16" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX16" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY16" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ16" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -9782,83 +9734,83 @@
         <v>13</v>
       </c>
       <c r="B17" s="61">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="C17" s="56">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>25.22</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>52</v>
       </c>
       <c r="E17" s="67" cm="1">
-        <f t="array" ref="E17">_xlfn.XLOOKUP($D17&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>0</v>
+        <f t="array" ref="E17">_xlfn.XLOOKUP($D17&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>25.22</v>
       </c>
       <c r="F17" s="67" cm="1">
-        <f t="array" ref="F17">_xlfn.XLOOKUP($D17&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F17">_xlfn.XLOOKUP($D17&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G17" s="67" cm="1">
-        <f t="array" ref="G17">_xlfn.XLOOKUP($D17&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G17">_xlfn.XLOOKUP($D17&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H17" s="67" cm="1">
-        <f t="array" ref="H17">_xlfn.XLOOKUP($D17&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H17">_xlfn.XLOOKUP($D17&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I17" s="67" cm="1">
-        <f t="array" ref="I17">_xlfn.XLOOKUP($D17&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I17">_xlfn.XLOOKUP($D17&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J17" s="67" cm="1">
-        <f t="array" ref="J17">_xlfn.XLOOKUP($D17&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J17">_xlfn.XLOOKUP($D17&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K17" s="67" cm="1">
-        <f t="array" ref="K17">_xlfn.XLOOKUP($D17&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K17">_xlfn.XLOOKUP($D17&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L17" s="67" cm="1">
-        <f t="array" ref="L17">_xlfn.XLOOKUP($D17&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L17">_xlfn.XLOOKUP($D17&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M17" s="67" cm="1">
-        <f t="array" ref="M17">_xlfn.XLOOKUP($D17&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M17">_xlfn.XLOOKUP($D17&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N17" s="67" cm="1">
-        <f t="array" ref="N17">_xlfn.XLOOKUP($D17&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N17">_xlfn.XLOOKUP($D17&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O17" s="67" cm="1">
-        <f t="array" ref="O17">_xlfn.XLOOKUP($D17&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O17">_xlfn.XLOOKUP($D17&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P17" s="67" cm="1">
-        <f t="array" ref="P17">_xlfn.XLOOKUP($D17&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P17">_xlfn.XLOOKUP($D17&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q17" s="67" cm="1">
-        <f t="array" ref="Q17">_xlfn.XLOOKUP($D17&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q17">_xlfn.XLOOKUP($D17&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R17" s="67" cm="1">
-        <f t="array" ref="R17">_xlfn.XLOOKUP($D17&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R17">_xlfn.XLOOKUP($D17&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S17" s="67" cm="1">
-        <f t="array" ref="S17">_xlfn.XLOOKUP($D17&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S17">_xlfn.XLOOKUP($D17&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z17" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>12</v>
       </c>
       <c r="AA17" s="2">
-        <f t="shared" ca="1" si="5"/>
-        <v>9999</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>12</v>
       </c>
       <c r="AB17">
         <f t="shared" si="23"/>
@@ -9897,67 +9849,67 @@
         <v>0</v>
       </c>
       <c r="AK17">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="AL17" s="1">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="AM17" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN17" s="1">
         <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="AL17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="1">
         <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="AM17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP17" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN17" s="1">
+      <c r="AQ17" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO17" s="1">
+      <c r="AR17" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP17" s="1">
+      <c r="AS17" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ17" s="1">
+      <c r="AT17" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR17" s="1">
+      <c r="AU17" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS17" s="1">
+      <c r="AV17" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT17" s="1">
+      <c r="AW17" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU17" s="1">
+      <c r="AX17" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV17" s="1">
+      <c r="AY17" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW17" s="1">
+      <c r="AZ17" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX17" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY17" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ17" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -9966,82 +9918,82 @@
         <v>14</v>
       </c>
       <c r="B18" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="C18" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>63</v>
       </c>
       <c r="E18" s="67" cm="1">
-        <f t="array" ref="E18">_xlfn.XLOOKUP($D18&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="E18">_xlfn.XLOOKUP($D18&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="F18" s="67" cm="1">
-        <f t="array" ref="F18">_xlfn.XLOOKUP($D18&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F18">_xlfn.XLOOKUP($D18&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G18" s="67" cm="1">
-        <f t="array" ref="G18">_xlfn.XLOOKUP($D18&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G18">_xlfn.XLOOKUP($D18&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H18" s="67" cm="1">
-        <f t="array" ref="H18">_xlfn.XLOOKUP($D18&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H18">_xlfn.XLOOKUP($D18&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I18" s="67" cm="1">
-        <f t="array" ref="I18">_xlfn.XLOOKUP($D18&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I18">_xlfn.XLOOKUP($D18&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J18" s="67" cm="1">
-        <f t="array" ref="J18">_xlfn.XLOOKUP($D18&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J18">_xlfn.XLOOKUP($D18&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K18" s="67" cm="1">
-        <f t="array" ref="K18">_xlfn.XLOOKUP($D18&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K18">_xlfn.XLOOKUP($D18&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L18" s="67" cm="1">
-        <f t="array" ref="L18">_xlfn.XLOOKUP($D18&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L18">_xlfn.XLOOKUP($D18&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M18" s="67" cm="1">
-        <f t="array" ref="M18">_xlfn.XLOOKUP($D18&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M18">_xlfn.XLOOKUP($D18&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N18" s="67" cm="1">
-        <f t="array" ref="N18">_xlfn.XLOOKUP($D18&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N18">_xlfn.XLOOKUP($D18&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O18" s="67" cm="1">
-        <f t="array" ref="O18">_xlfn.XLOOKUP($D18&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O18">_xlfn.XLOOKUP($D18&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P18" s="67" cm="1">
-        <f t="array" ref="P18">_xlfn.XLOOKUP($D18&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P18">_xlfn.XLOOKUP($D18&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q18" s="67" cm="1">
-        <f t="array" ref="Q18">_xlfn.XLOOKUP($D18&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q18">_xlfn.XLOOKUP($D18&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R18" s="67" cm="1">
-        <f t="array" ref="R18">_xlfn.XLOOKUP($D18&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R18">_xlfn.XLOOKUP($D18&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S18" s="67" cm="1">
-        <f t="array" ref="S18">_xlfn.XLOOKUP($D18&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S18">_xlfn.XLOOKUP($D18&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z18" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="AA18" s="2">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="22"/>
         <v>9999</v>
       </c>
       <c r="AB18">
@@ -10081,67 +10033,67 @@
         <v>0</v>
       </c>
       <c r="AK18">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL18" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM18" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN18" s="1">
         <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="AL18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="1">
         <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="AM18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP18" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN18" s="1">
+      <c r="AQ18" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO18" s="1">
+      <c r="AR18" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP18" s="1">
+      <c r="AS18" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ18" s="1">
+      <c r="AT18" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR18" s="1">
+      <c r="AU18" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS18" s="1">
+      <c r="AV18" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT18" s="1">
+      <c r="AW18" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU18" s="1">
+      <c r="AX18" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV18" s="1">
+      <c r="AY18" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW18" s="1">
+      <c r="AZ18" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX18" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY18" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ18" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10150,82 +10102,82 @@
         <v>15</v>
       </c>
       <c r="B19" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="C19" s="56">
-        <f t="shared" si="3"/>
-        <v>31.01</v>
+        <f t="shared" si="21"/>
+        <v>31.32</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>36</v>
       </c>
       <c r="E19" s="67" cm="1">
-        <f t="array" ref="E19">_xlfn.XLOOKUP($D19&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>31.01</v>
+        <f t="array" ref="E19">_xlfn.XLOOKUP($D19&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>31.32</v>
       </c>
       <c r="F19" s="67" cm="1">
-        <f t="array" ref="F19">_xlfn.XLOOKUP($D19&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F19">_xlfn.XLOOKUP($D19&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G19" s="67" cm="1">
-        <f t="array" ref="G19">_xlfn.XLOOKUP($D19&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G19">_xlfn.XLOOKUP($D19&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H19" s="67" cm="1">
-        <f t="array" ref="H19">_xlfn.XLOOKUP($D19&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H19">_xlfn.XLOOKUP($D19&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I19" s="67" cm="1">
-        <f t="array" ref="I19">_xlfn.XLOOKUP($D19&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I19">_xlfn.XLOOKUP($D19&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J19" s="67" cm="1">
-        <f t="array" ref="J19">_xlfn.XLOOKUP($D19&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J19">_xlfn.XLOOKUP($D19&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K19" s="67" cm="1">
-        <f t="array" ref="K19">_xlfn.XLOOKUP($D19&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K19">_xlfn.XLOOKUP($D19&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L19" s="67" cm="1">
-        <f t="array" ref="L19">_xlfn.XLOOKUP($D19&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L19">_xlfn.XLOOKUP($D19&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M19" s="67" cm="1">
-        <f t="array" ref="M19">_xlfn.XLOOKUP($D19&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M19">_xlfn.XLOOKUP($D19&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N19" s="67" cm="1">
-        <f t="array" ref="N19">_xlfn.XLOOKUP($D19&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N19">_xlfn.XLOOKUP($D19&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O19" s="67" cm="1">
-        <f t="array" ref="O19">_xlfn.XLOOKUP($D19&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O19">_xlfn.XLOOKUP($D19&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P19" s="67" cm="1">
-        <f t="array" ref="P19">_xlfn.XLOOKUP($D19&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P19">_xlfn.XLOOKUP($D19&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q19" s="67" cm="1">
-        <f t="array" ref="Q19">_xlfn.XLOOKUP($D19&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q19">_xlfn.XLOOKUP($D19&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R19" s="67" cm="1">
-        <f t="array" ref="R19">_xlfn.XLOOKUP($D19&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R19">_xlfn.XLOOKUP($D19&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S19" s="67" cm="1">
-        <f t="array" ref="S19">_xlfn.XLOOKUP($D19&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S19">_xlfn.XLOOKUP($D19&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z19" s="5">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="2"/>
         <v>4</v>
       </c>
       <c r="AA19" s="2">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="22"/>
         <v>4</v>
       </c>
       <c r="AB19">
@@ -10265,67 +10217,67 @@
         <v>0</v>
       </c>
       <c r="AK19">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AL19" s="1">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AM19" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN19" s="1">
         <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="AL19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="1">
         <f t="shared" si="8"/>
-        <v>4</v>
-      </c>
-      <c r="AM19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP19" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN19" s="1">
+      <c r="AQ19" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO19" s="1">
+      <c r="AR19" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP19" s="1">
+      <c r="AS19" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ19" s="1">
+      <c r="AT19" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR19" s="1">
+      <c r="AU19" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS19" s="1">
+      <c r="AV19" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT19" s="1">
+      <c r="AW19" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU19" s="1">
+      <c r="AX19" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV19" s="1">
+      <c r="AY19" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW19" s="1">
+      <c r="AZ19" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX19" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY19" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ19" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10334,83 +10286,83 @@
         <v>16</v>
       </c>
       <c r="B20" s="61">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="C20" s="56">
-        <f t="shared" si="3"/>
-        <v>31.2</v>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>35</v>
       </c>
       <c r="E20" s="67" cm="1">
-        <f t="array" ref="E20">_xlfn.XLOOKUP($D20&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>31.2</v>
+        <f t="array" ref="E20">_xlfn.XLOOKUP($D20&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>0</v>
       </c>
       <c r="F20" s="67" cm="1">
-        <f t="array" ref="F20">_xlfn.XLOOKUP($D20&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F20">_xlfn.XLOOKUP($D20&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G20" s="67" cm="1">
-        <f t="array" ref="G20">_xlfn.XLOOKUP($D20&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G20">_xlfn.XLOOKUP($D20&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H20" s="67" cm="1">
-        <f t="array" ref="H20">_xlfn.XLOOKUP($D20&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H20">_xlfn.XLOOKUP($D20&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I20" s="67" cm="1">
-        <f t="array" ref="I20">_xlfn.XLOOKUP($D20&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I20">_xlfn.XLOOKUP($D20&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J20" s="67" cm="1">
-        <f t="array" ref="J20">_xlfn.XLOOKUP($D20&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J20">_xlfn.XLOOKUP($D20&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K20" s="67" cm="1">
-        <f t="array" ref="K20">_xlfn.XLOOKUP($D20&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K20">_xlfn.XLOOKUP($D20&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L20" s="67" cm="1">
-        <f t="array" ref="L20">_xlfn.XLOOKUP($D20&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L20">_xlfn.XLOOKUP($D20&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M20" s="67" cm="1">
-        <f t="array" ref="M20">_xlfn.XLOOKUP($D20&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M20">_xlfn.XLOOKUP($D20&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N20" s="67" cm="1">
-        <f t="array" ref="N20">_xlfn.XLOOKUP($D20&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N20">_xlfn.XLOOKUP($D20&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O20" s="67" cm="1">
-        <f t="array" ref="O20">_xlfn.XLOOKUP($D20&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O20">_xlfn.XLOOKUP($D20&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P20" s="67" cm="1">
-        <f t="array" ref="P20">_xlfn.XLOOKUP($D20&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P20">_xlfn.XLOOKUP($D20&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q20" s="67" cm="1">
-        <f t="array" ref="Q20">_xlfn.XLOOKUP($D20&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q20">_xlfn.XLOOKUP($D20&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R20" s="67" cm="1">
-        <f t="array" ref="R20">_xlfn.XLOOKUP($D20&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R20">_xlfn.XLOOKUP($D20&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S20" s="67" cm="1">
-        <f t="array" ref="S20">_xlfn.XLOOKUP($D20&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S20">_xlfn.XLOOKUP($D20&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z20" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="AA20" s="2">
-        <f t="shared" ca="1" si="5"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>9999</v>
       </c>
       <c r="AB20">
         <f t="shared" si="23"/>
@@ -10449,67 +10401,67 @@
         <v>0</v>
       </c>
       <c r="AK20">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL20" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM20" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN20" s="1">
         <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="AL20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="1">
         <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="AM20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN20" s="1">
+      <c r="AQ20" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO20" s="1">
+      <c r="AR20" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP20" s="1">
+      <c r="AS20" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ20" s="1">
+      <c r="AT20" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR20" s="1">
+      <c r="AU20" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS20" s="1">
+      <c r="AV20" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT20" s="1">
+      <c r="AW20" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU20" s="1">
+      <c r="AX20" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV20" s="1">
+      <c r="AY20" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW20" s="1">
+      <c r="AZ20" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX20" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY20" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ20" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10518,83 +10470,83 @@
         <v>17</v>
       </c>
       <c r="B21" s="61">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="C21" s="56">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>24.02</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>62</v>
       </c>
       <c r="E21" s="67" cm="1">
-        <f t="array" ref="E21">_xlfn.XLOOKUP($D21&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>0</v>
+        <f t="array" ref="E21">_xlfn.XLOOKUP($D21&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>24.02</v>
       </c>
       <c r="F21" s="67" cm="1">
-        <f t="array" ref="F21">_xlfn.XLOOKUP($D21&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F21">_xlfn.XLOOKUP($D21&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G21" s="67" cm="1">
-        <f t="array" ref="G21">_xlfn.XLOOKUP($D21&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G21">_xlfn.XLOOKUP($D21&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H21" s="67" cm="1">
-        <f t="array" ref="H21">_xlfn.XLOOKUP($D21&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H21">_xlfn.XLOOKUP($D21&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I21" s="67" cm="1">
-        <f t="array" ref="I21">_xlfn.XLOOKUP($D21&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I21">_xlfn.XLOOKUP($D21&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J21" s="67" cm="1">
-        <f t="array" ref="J21">_xlfn.XLOOKUP($D21&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J21">_xlfn.XLOOKUP($D21&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K21" s="67" cm="1">
-        <f t="array" ref="K21">_xlfn.XLOOKUP($D21&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K21">_xlfn.XLOOKUP($D21&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L21" s="67" cm="1">
-        <f t="array" ref="L21">_xlfn.XLOOKUP($D21&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L21">_xlfn.XLOOKUP($D21&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M21" s="67" cm="1">
-        <f t="array" ref="M21">_xlfn.XLOOKUP($D21&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M21">_xlfn.XLOOKUP($D21&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N21" s="67" cm="1">
-        <f t="array" ref="N21">_xlfn.XLOOKUP($D21&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N21">_xlfn.XLOOKUP($D21&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O21" s="67" cm="1">
-        <f t="array" ref="O21">_xlfn.XLOOKUP($D21&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O21">_xlfn.XLOOKUP($D21&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P21" s="67" cm="1">
-        <f t="array" ref="P21">_xlfn.XLOOKUP($D21&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P21">_xlfn.XLOOKUP($D21&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q21" s="67" cm="1">
-        <f t="array" ref="Q21">_xlfn.XLOOKUP($D21&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q21">_xlfn.XLOOKUP($D21&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R21" s="67" cm="1">
-        <f t="array" ref="R21">_xlfn.XLOOKUP($D21&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R21">_xlfn.XLOOKUP($D21&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S21" s="67" cm="1">
-        <f t="array" ref="S21">_xlfn.XLOOKUP($D21&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S21">_xlfn.XLOOKUP($D21&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z21" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>13</v>
       </c>
       <c r="AA21" s="2">
-        <f t="shared" ca="1" si="5"/>
-        <v>9999</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>13</v>
       </c>
       <c r="AB21">
         <f t="shared" si="23"/>
@@ -10633,67 +10585,67 @@
         <v>0</v>
       </c>
       <c r="AK21">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="AL21" s="1">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="AM21" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN21" s="1">
         <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="AL21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO21" s="1">
         <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="AM21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP21" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN21" s="1">
+      <c r="AQ21" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO21" s="1">
+      <c r="AR21" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP21" s="1">
+      <c r="AS21" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ21" s="1">
+      <c r="AT21" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR21" s="1">
+      <c r="AU21" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS21" s="1">
+      <c r="AV21" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT21" s="1">
+      <c r="AW21" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU21" s="1">
+      <c r="AX21" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV21" s="1">
+      <c r="AY21" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW21" s="1">
+      <c r="AZ21" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX21" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY21" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ21" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10702,82 +10654,82 @@
         <v>18</v>
       </c>
       <c r="B22" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="C22" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>64</v>
       </c>
       <c r="E22" s="67" cm="1">
-        <f t="array" ref="E22">_xlfn.XLOOKUP($D22&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="E22">_xlfn.XLOOKUP($D22&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="F22" s="67" cm="1">
-        <f t="array" ref="F22">_xlfn.XLOOKUP($D22&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F22">_xlfn.XLOOKUP($D22&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G22" s="67" cm="1">
-        <f t="array" ref="G22">_xlfn.XLOOKUP($D22&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G22">_xlfn.XLOOKUP($D22&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H22" s="67" cm="1">
-        <f t="array" ref="H22">_xlfn.XLOOKUP($D22&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H22">_xlfn.XLOOKUP($D22&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I22" s="67" cm="1">
-        <f t="array" ref="I22">_xlfn.XLOOKUP($D22&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I22">_xlfn.XLOOKUP($D22&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J22" s="67" cm="1">
-        <f t="array" ref="J22">_xlfn.XLOOKUP($D22&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J22">_xlfn.XLOOKUP($D22&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K22" s="67" cm="1">
-        <f t="array" ref="K22">_xlfn.XLOOKUP($D22&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K22">_xlfn.XLOOKUP($D22&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L22" s="67" cm="1">
-        <f t="array" ref="L22">_xlfn.XLOOKUP($D22&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L22">_xlfn.XLOOKUP($D22&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M22" s="67" cm="1">
-        <f t="array" ref="M22">_xlfn.XLOOKUP($D22&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M22">_xlfn.XLOOKUP($D22&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N22" s="67" cm="1">
-        <f t="array" ref="N22">_xlfn.XLOOKUP($D22&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N22">_xlfn.XLOOKUP($D22&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O22" s="67" cm="1">
-        <f t="array" ref="O22">_xlfn.XLOOKUP($D22&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O22">_xlfn.XLOOKUP($D22&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P22" s="67" cm="1">
-        <f t="array" ref="P22">_xlfn.XLOOKUP($D22&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P22">_xlfn.XLOOKUP($D22&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q22" s="67" cm="1">
-        <f t="array" ref="Q22">_xlfn.XLOOKUP($D22&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q22">_xlfn.XLOOKUP($D22&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R22" s="67" cm="1">
-        <f t="array" ref="R22">_xlfn.XLOOKUP($D22&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R22">_xlfn.XLOOKUP($D22&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S22" s="67" cm="1">
-        <f t="array" ref="S22">_xlfn.XLOOKUP($D22&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S22">_xlfn.XLOOKUP($D22&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z22" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="AA22" s="2">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="22"/>
         <v>9999</v>
       </c>
       <c r="AB22">
@@ -10817,67 +10769,67 @@
         <v>0</v>
       </c>
       <c r="AK22">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL22" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM22" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN22" s="1">
         <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="AL22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="1">
         <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="AM22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN22" s="1">
+      <c r="AQ22" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO22" s="1">
+      <c r="AR22" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP22" s="1">
+      <c r="AS22" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ22" s="1">
+      <c r="AT22" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR22" s="1">
+      <c r="AU22" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS22" s="1">
+      <c r="AV22" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT22" s="1">
+      <c r="AW22" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU22" s="1">
+      <c r="AX22" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV22" s="1">
+      <c r="AY22" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW22" s="1">
+      <c r="AZ22" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX22" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY22" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ22" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10886,83 +10838,83 @@
         <v>19</v>
       </c>
       <c r="B23" s="61">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="C23" s="56">
-        <f t="shared" si="3"/>
-        <v>34.75</v>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>33</v>
       </c>
       <c r="E23" s="67" cm="1">
-        <f t="array" ref="E23">_xlfn.XLOOKUP($D23&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>34.75</v>
+        <f t="array" ref="E23">_xlfn.XLOOKUP($D23&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>0</v>
       </c>
       <c r="F23" s="67" cm="1">
-        <f t="array" ref="F23">_xlfn.XLOOKUP($D23&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F23">_xlfn.XLOOKUP($D23&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G23" s="67" cm="1">
-        <f t="array" ref="G23">_xlfn.XLOOKUP($D23&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G23">_xlfn.XLOOKUP($D23&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H23" s="67" cm="1">
-        <f t="array" ref="H23">_xlfn.XLOOKUP($D23&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H23">_xlfn.XLOOKUP($D23&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I23" s="67" cm="1">
-        <f t="array" ref="I23">_xlfn.XLOOKUP($D23&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I23">_xlfn.XLOOKUP($D23&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J23" s="67" cm="1">
-        <f t="array" ref="J23">_xlfn.XLOOKUP($D23&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J23">_xlfn.XLOOKUP($D23&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K23" s="67" cm="1">
-        <f t="array" ref="K23">_xlfn.XLOOKUP($D23&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K23">_xlfn.XLOOKUP($D23&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L23" s="67" cm="1">
-        <f t="array" ref="L23">_xlfn.XLOOKUP($D23&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L23">_xlfn.XLOOKUP($D23&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M23" s="67" cm="1">
-        <f t="array" ref="M23">_xlfn.XLOOKUP($D23&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M23">_xlfn.XLOOKUP($D23&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N23" s="67" cm="1">
-        <f t="array" ref="N23">_xlfn.XLOOKUP($D23&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N23">_xlfn.XLOOKUP($D23&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O23" s="67" cm="1">
-        <f t="array" ref="O23">_xlfn.XLOOKUP($D23&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O23">_xlfn.XLOOKUP($D23&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P23" s="67" cm="1">
-        <f t="array" ref="P23">_xlfn.XLOOKUP($D23&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P23">_xlfn.XLOOKUP($D23&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q23" s="67" cm="1">
-        <f t="array" ref="Q23">_xlfn.XLOOKUP($D23&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q23">_xlfn.XLOOKUP($D23&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R23" s="67" cm="1">
-        <f t="array" ref="R23">_xlfn.XLOOKUP($D23&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R23">_xlfn.XLOOKUP($D23&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S23" s="67" cm="1">
-        <f t="array" ref="S23">_xlfn.XLOOKUP($D23&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S23">_xlfn.XLOOKUP($D23&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z23" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="AA23" s="2">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>9999</v>
       </c>
       <c r="AB23">
         <f t="shared" si="23"/>
@@ -11001,67 +10953,67 @@
         <v>0</v>
       </c>
       <c r="AK23">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL23" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM23" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN23" s="1">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="AL23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="1">
         <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AM23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP23" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN23" s="1">
+      <c r="AQ23" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO23" s="1">
+      <c r="AR23" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP23" s="1">
+      <c r="AS23" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ23" s="1">
+      <c r="AT23" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR23" s="1">
+      <c r="AU23" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS23" s="1">
+      <c r="AV23" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT23" s="1">
+      <c r="AW23" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU23" s="1">
+      <c r="AX23" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV23" s="1">
+      <c r="AY23" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW23" s="1">
+      <c r="AZ23" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX23" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY23" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ23" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -11070,82 +11022,82 @@
         <v>20</v>
       </c>
       <c r="B24" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="C24" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>57</v>
       </c>
       <c r="E24" s="67" cm="1">
-        <f t="array" ref="E24">_xlfn.XLOOKUP($D24&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="E24">_xlfn.XLOOKUP($D24&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="F24" s="67" cm="1">
-        <f t="array" ref="F24">_xlfn.XLOOKUP($D24&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F24">_xlfn.XLOOKUP($D24&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G24" s="67" cm="1">
-        <f t="array" ref="G24">_xlfn.XLOOKUP($D24&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G24">_xlfn.XLOOKUP($D24&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H24" s="67" cm="1">
-        <f t="array" ref="H24">_xlfn.XLOOKUP($D24&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H24">_xlfn.XLOOKUP($D24&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I24" s="67" cm="1">
-        <f t="array" ref="I24">_xlfn.XLOOKUP($D24&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I24">_xlfn.XLOOKUP($D24&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J24" s="67" cm="1">
-        <f t="array" ref="J24">_xlfn.XLOOKUP($D24&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J24">_xlfn.XLOOKUP($D24&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K24" s="67" cm="1">
-        <f t="array" ref="K24">_xlfn.XLOOKUP($D24&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K24">_xlfn.XLOOKUP($D24&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L24" s="67" cm="1">
-        <f t="array" ref="L24">_xlfn.XLOOKUP($D24&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L24">_xlfn.XLOOKUP($D24&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M24" s="67" cm="1">
-        <f t="array" ref="M24">_xlfn.XLOOKUP($D24&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M24">_xlfn.XLOOKUP($D24&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N24" s="67" cm="1">
-        <f t="array" ref="N24">_xlfn.XLOOKUP($D24&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N24">_xlfn.XLOOKUP($D24&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O24" s="67" cm="1">
-        <f t="array" ref="O24">_xlfn.XLOOKUP($D24&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O24">_xlfn.XLOOKUP($D24&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P24" s="67" cm="1">
-        <f t="array" ref="P24">_xlfn.XLOOKUP($D24&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P24">_xlfn.XLOOKUP($D24&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q24" s="67" cm="1">
-        <f t="array" ref="Q24">_xlfn.XLOOKUP($D24&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q24">_xlfn.XLOOKUP($D24&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R24" s="67" cm="1">
-        <f t="array" ref="R24">_xlfn.XLOOKUP($D24&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R24">_xlfn.XLOOKUP($D24&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S24" s="67" cm="1">
-        <f t="array" ref="S24">_xlfn.XLOOKUP($D24&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S24">_xlfn.XLOOKUP($D24&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z24" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="AA24" s="2">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="22"/>
         <v>9999</v>
       </c>
       <c r="AB24">
@@ -11185,67 +11137,67 @@
         <v>0</v>
       </c>
       <c r="AK24">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL24" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM24" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN24" s="1">
         <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="AL24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="1">
         <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="AM24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP24" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN24" s="1">
+      <c r="AQ24" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO24" s="1">
+      <c r="AR24" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP24" s="1">
+      <c r="AS24" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ24" s="1">
+      <c r="AT24" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR24" s="1">
+      <c r="AU24" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS24" s="1">
+      <c r="AV24" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT24" s="1">
+      <c r="AW24" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU24" s="1">
+      <c r="AX24" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV24" s="1">
+      <c r="AY24" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW24" s="1">
+      <c r="AZ24" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX24" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY24" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ24" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -11254,82 +11206,82 @@
         <v>21</v>
       </c>
       <c r="B25" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="C25" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>60</v>
       </c>
       <c r="E25" s="67" cm="1">
-        <f t="array" ref="E25">_xlfn.XLOOKUP($D25&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="E25">_xlfn.XLOOKUP($D25&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="F25" s="67" cm="1">
-        <f t="array" ref="F25">_xlfn.XLOOKUP($D25&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F25">_xlfn.XLOOKUP($D25&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G25" s="67" cm="1">
-        <f t="array" ref="G25">_xlfn.XLOOKUP($D25&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G25">_xlfn.XLOOKUP($D25&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H25" s="67" cm="1">
-        <f t="array" ref="H25">_xlfn.XLOOKUP($D25&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H25">_xlfn.XLOOKUP($D25&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I25" s="67" cm="1">
-        <f t="array" ref="I25">_xlfn.XLOOKUP($D25&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I25">_xlfn.XLOOKUP($D25&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J25" s="67" cm="1">
-        <f t="array" ref="J25">_xlfn.XLOOKUP($D25&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J25">_xlfn.XLOOKUP($D25&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K25" s="67" cm="1">
-        <f t="array" ref="K25">_xlfn.XLOOKUP($D25&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K25">_xlfn.XLOOKUP($D25&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L25" s="67" cm="1">
-        <f t="array" ref="L25">_xlfn.XLOOKUP($D25&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L25">_xlfn.XLOOKUP($D25&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M25" s="67" cm="1">
-        <f t="array" ref="M25">_xlfn.XLOOKUP($D25&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M25">_xlfn.XLOOKUP($D25&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N25" s="67" cm="1">
-        <f t="array" ref="N25">_xlfn.XLOOKUP($D25&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N25">_xlfn.XLOOKUP($D25&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O25" s="67" cm="1">
-        <f t="array" ref="O25">_xlfn.XLOOKUP($D25&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O25">_xlfn.XLOOKUP($D25&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P25" s="67" cm="1">
-        <f t="array" ref="P25">_xlfn.XLOOKUP($D25&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P25">_xlfn.XLOOKUP($D25&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q25" s="67" cm="1">
-        <f t="array" ref="Q25">_xlfn.XLOOKUP($D25&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q25">_xlfn.XLOOKUP($D25&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R25" s="67" cm="1">
-        <f t="array" ref="R25">_xlfn.XLOOKUP($D25&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R25">_xlfn.XLOOKUP($D25&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S25" s="67" cm="1">
-        <f t="array" ref="S25">_xlfn.XLOOKUP($D25&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S25">_xlfn.XLOOKUP($D25&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z25" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="AA25" s="2">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="22"/>
         <v>9999</v>
       </c>
       <c r="AB25">
@@ -11369,67 +11321,67 @@
         <v>0</v>
       </c>
       <c r="AK25">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL25" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM25" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN25" s="1">
         <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="AL25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="1">
         <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="AM25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN25" s="1">
+      <c r="AQ25" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO25" s="1">
+      <c r="AR25" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP25" s="1">
+      <c r="AS25" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ25" s="1">
+      <c r="AT25" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR25" s="1">
+      <c r="AU25" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS25" s="1">
+      <c r="AV25" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT25" s="1">
+      <c r="AW25" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU25" s="1">
+      <c r="AX25" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV25" s="1">
+      <c r="AY25" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW25" s="1">
+      <c r="AZ25" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX25" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY25" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ25" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -11438,82 +11390,82 @@
         <v>22</v>
       </c>
       <c r="B26" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="C26" s="56">
-        <f t="shared" si="3"/>
-        <v>29.41</v>
+        <f t="shared" si="21"/>
+        <v>30.09</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>50</v>
       </c>
       <c r="E26" s="67" cm="1">
-        <f t="array" ref="E26">_xlfn.XLOOKUP($D26&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>29.41</v>
+        <f t="array" ref="E26">_xlfn.XLOOKUP($D26&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>30.09</v>
       </c>
       <c r="F26" s="67" cm="1">
-        <f t="array" ref="F26">_xlfn.XLOOKUP($D26&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F26">_xlfn.XLOOKUP($D26&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G26" s="67" cm="1">
-        <f t="array" ref="G26">_xlfn.XLOOKUP($D26&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G26">_xlfn.XLOOKUP($D26&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H26" s="67" cm="1">
-        <f t="array" ref="H26">_xlfn.XLOOKUP($D26&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H26">_xlfn.XLOOKUP($D26&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I26" s="67" cm="1">
-        <f t="array" ref="I26">_xlfn.XLOOKUP($D26&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I26">_xlfn.XLOOKUP($D26&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J26" s="67" cm="1">
-        <f t="array" ref="J26">_xlfn.XLOOKUP($D26&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J26">_xlfn.XLOOKUP($D26&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K26" s="67" cm="1">
-        <f t="array" ref="K26">_xlfn.XLOOKUP($D26&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K26">_xlfn.XLOOKUP($D26&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L26" s="67" cm="1">
-        <f t="array" ref="L26">_xlfn.XLOOKUP($D26&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L26">_xlfn.XLOOKUP($D26&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M26" s="67" cm="1">
-        <f t="array" ref="M26">_xlfn.XLOOKUP($D26&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M26">_xlfn.XLOOKUP($D26&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N26" s="67" cm="1">
-        <f t="array" ref="N26">_xlfn.XLOOKUP($D26&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N26">_xlfn.XLOOKUP($D26&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O26" s="67" cm="1">
-        <f t="array" ref="O26">_xlfn.XLOOKUP($D26&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O26">_xlfn.XLOOKUP($D26&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P26" s="67" cm="1">
-        <f t="array" ref="P26">_xlfn.XLOOKUP($D26&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P26">_xlfn.XLOOKUP($D26&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q26" s="67" cm="1">
-        <f t="array" ref="Q26">_xlfn.XLOOKUP($D26&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q26">_xlfn.XLOOKUP($D26&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R26" s="67" cm="1">
-        <f t="array" ref="R26">_xlfn.XLOOKUP($D26&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R26">_xlfn.XLOOKUP($D26&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S26" s="67" cm="1">
-        <f t="array" ref="S26">_xlfn.XLOOKUP($D26&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S26">_xlfn.XLOOKUP($D26&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z26" s="5">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="2"/>
         <v>8</v>
       </c>
       <c r="AA26" s="2">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="22"/>
         <v>8</v>
       </c>
       <c r="AB26">
@@ -11553,67 +11505,67 @@
         <v>0</v>
       </c>
       <c r="AK26">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="AL26" s="1">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AM26" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN26" s="1">
         <f t="shared" si="7"/>
-        <v>8</v>
-      </c>
-      <c r="AL26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="1">
         <f t="shared" si="8"/>
-        <v>8</v>
-      </c>
-      <c r="AM26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP26" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN26" s="1">
+      <c r="AQ26" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO26" s="1">
+      <c r="AR26" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP26" s="1">
+      <c r="AS26" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ26" s="1">
+      <c r="AT26" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR26" s="1">
+      <c r="AU26" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS26" s="1">
+      <c r="AV26" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT26" s="1">
+      <c r="AW26" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU26" s="1">
+      <c r="AX26" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV26" s="1">
+      <c r="AY26" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW26" s="1">
+      <c r="AZ26" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX26" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY26" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ26" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -11622,83 +11574,83 @@
         <v>23</v>
       </c>
       <c r="B27" s="61">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="C27" s="56">
-        <f t="shared" si="3"/>
-        <v>27.73</v>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>45</v>
       </c>
       <c r="E27" s="67" cm="1">
-        <f t="array" ref="E27">_xlfn.XLOOKUP($D27&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>27.73</v>
+        <f t="array" ref="E27">_xlfn.XLOOKUP($D27&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>0</v>
       </c>
       <c r="F27" s="67" cm="1">
-        <f t="array" ref="F27">_xlfn.XLOOKUP($D27&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F27">_xlfn.XLOOKUP($D27&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G27" s="67" cm="1">
-        <f t="array" ref="G27">_xlfn.XLOOKUP($D27&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G27">_xlfn.XLOOKUP($D27&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H27" s="67" cm="1">
-        <f t="array" ref="H27">_xlfn.XLOOKUP($D27&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H27">_xlfn.XLOOKUP($D27&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I27" s="67" cm="1">
-        <f t="array" ref="I27">_xlfn.XLOOKUP($D27&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I27">_xlfn.XLOOKUP($D27&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J27" s="67" cm="1">
-        <f t="array" ref="J27">_xlfn.XLOOKUP($D27&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J27">_xlfn.XLOOKUP($D27&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K27" s="67" cm="1">
-        <f t="array" ref="K27">_xlfn.XLOOKUP($D27&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K27">_xlfn.XLOOKUP($D27&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L27" s="67" cm="1">
-        <f t="array" ref="L27">_xlfn.XLOOKUP($D27&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L27">_xlfn.XLOOKUP($D27&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M27" s="67" cm="1">
-        <f t="array" ref="M27">_xlfn.XLOOKUP($D27&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M27">_xlfn.XLOOKUP($D27&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N27" s="67" cm="1">
-        <f t="array" ref="N27">_xlfn.XLOOKUP($D27&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N27">_xlfn.XLOOKUP($D27&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O27" s="67" cm="1">
-        <f t="array" ref="O27">_xlfn.XLOOKUP($D27&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O27">_xlfn.XLOOKUP($D27&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P27" s="67" cm="1">
-        <f t="array" ref="P27">_xlfn.XLOOKUP($D27&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P27">_xlfn.XLOOKUP($D27&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q27" s="67" cm="1">
-        <f t="array" ref="Q27">_xlfn.XLOOKUP($D27&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q27">_xlfn.XLOOKUP($D27&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R27" s="67" cm="1">
-        <f t="array" ref="R27">_xlfn.XLOOKUP($D27&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R27">_xlfn.XLOOKUP($D27&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S27" s="67" cm="1">
-        <f t="array" ref="S27">_xlfn.XLOOKUP($D27&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S27">_xlfn.XLOOKUP($D27&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z27" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>12</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="AA27" s="2">
-        <f t="shared" ca="1" si="5"/>
-        <v>12</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>9999</v>
       </c>
       <c r="AB27">
         <f t="shared" si="23"/>
@@ -11737,67 +11689,67 @@
         <v>0</v>
       </c>
       <c r="AK27">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL27" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM27" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN27" s="1">
         <f t="shared" si="7"/>
-        <v>12</v>
-      </c>
-      <c r="AL27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="1">
         <f t="shared" si="8"/>
-        <v>12</v>
-      </c>
-      <c r="AM27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP27" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN27" s="1">
+      <c r="AQ27" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO27" s="1">
+      <c r="AR27" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP27" s="1">
+      <c r="AS27" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ27" s="1">
+      <c r="AT27" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR27" s="1">
+      <c r="AU27" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS27" s="1">
+      <c r="AV27" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT27" s="1">
+      <c r="AW27" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU27" s="1">
+      <c r="AX27" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV27" s="1">
+      <c r="AY27" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW27" s="1">
+      <c r="AZ27" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX27" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY27" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ27" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -11806,83 +11758,83 @@
         <v>24</v>
       </c>
       <c r="B28" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="C28" s="56">
-        <f t="shared" si="3"/>
-        <v>29.71</v>
+        <f t="shared" si="21"/>
+        <v>30.01</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E28" s="67" cm="1">
-        <f t="array" ref="E28">_xlfn.XLOOKUP($D28&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>29.71</v>
+        <f t="array" ref="E28">_xlfn.XLOOKUP($D28&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>30.01</v>
       </c>
       <c r="F28" s="67" cm="1">
-        <f t="array" ref="F28">_xlfn.XLOOKUP($D28&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F28">_xlfn.XLOOKUP($D28&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G28" s="67" cm="1">
-        <f t="array" ref="G28">_xlfn.XLOOKUP($D28&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G28">_xlfn.XLOOKUP($D28&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H28" s="67" cm="1">
-        <f t="array" ref="H28">_xlfn.XLOOKUP($D28&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H28">_xlfn.XLOOKUP($D28&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I28" s="67" cm="1">
-        <f t="array" ref="I28">_xlfn.XLOOKUP($D28&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I28">_xlfn.XLOOKUP($D28&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J28" s="67" cm="1">
-        <f t="array" ref="J28">_xlfn.XLOOKUP($D28&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J28">_xlfn.XLOOKUP($D28&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K28" s="67" cm="1">
-        <f t="array" ref="K28">_xlfn.XLOOKUP($D28&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K28">_xlfn.XLOOKUP($D28&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L28" s="67" cm="1">
-        <f t="array" ref="L28">_xlfn.XLOOKUP($D28&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L28">_xlfn.XLOOKUP($D28&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M28" s="67" cm="1">
-        <f t="array" ref="M28">_xlfn.XLOOKUP($D28&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M28">_xlfn.XLOOKUP($D28&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N28" s="67" cm="1">
-        <f t="array" ref="N28">_xlfn.XLOOKUP($D28&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N28">_xlfn.XLOOKUP($D28&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O28" s="67" cm="1">
-        <f t="array" ref="O28">_xlfn.XLOOKUP($D28&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O28">_xlfn.XLOOKUP($D28&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P28" s="67" cm="1">
-        <f t="array" ref="P28">_xlfn.XLOOKUP($D28&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P28">_xlfn.XLOOKUP($D28&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q28" s="67" cm="1">
-        <f t="array" ref="Q28">_xlfn.XLOOKUP($D28&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q28">_xlfn.XLOOKUP($D28&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R28" s="67" cm="1">
-        <f t="array" ref="R28">_xlfn.XLOOKUP($D28&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R28">_xlfn.XLOOKUP($D28&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S28" s="67" cm="1">
-        <f t="array" ref="S28">_xlfn.XLOOKUP($D28&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S28">_xlfn.XLOOKUP($D28&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z28" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>6</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>9</v>
       </c>
       <c r="AA28" s="2">
-        <f t="shared" ca="1" si="5"/>
-        <v>6</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>9</v>
       </c>
       <c r="AB28">
         <f t="shared" ref="AB28:AJ28" si="30">AC28-LARGE($AL28:$AZ28,AB$3)</f>
@@ -11922,66 +11874,66 @@
       </c>
       <c r="AK28">
         <f>SUM(AL28:AZ28)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AL28" s="1">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="AM28" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN28" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AO28" s="1">
         <f t="shared" si="8"/>
-        <v>6</v>
-      </c>
-      <c r="AM28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN28" s="1">
+      <c r="AQ28" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO28" s="1">
+      <c r="AR28" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP28" s="1">
+      <c r="AS28" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ28" s="1">
+      <c r="AT28" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR28" s="1">
+      <c r="AU28" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS28" s="1">
+      <c r="AV28" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT28" s="1">
+      <c r="AW28" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU28" s="1">
+      <c r="AX28" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV28" s="1">
+      <c r="AY28" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW28" s="1">
+      <c r="AZ28" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX28" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY28" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ28" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -11990,83 +11942,83 @@
         <v>25</v>
       </c>
       <c r="B29" s="61">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="C29" s="56">
-        <f t="shared" si="3"/>
-        <v>25.4</v>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E29" s="67" cm="1">
-        <f t="array" ref="E29">_xlfn.XLOOKUP($D29&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>25.4</v>
+        <f t="array" ref="E29">_xlfn.XLOOKUP($D29&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>0</v>
       </c>
       <c r="F29" s="67" cm="1">
-        <f t="array" ref="F29">_xlfn.XLOOKUP($D29&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F29">_xlfn.XLOOKUP($D29&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G29" s="67" cm="1">
-        <f t="array" ref="G29">_xlfn.XLOOKUP($D29&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G29">_xlfn.XLOOKUP($D29&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H29" s="67" cm="1">
-        <f t="array" ref="H29">_xlfn.XLOOKUP($D29&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H29">_xlfn.XLOOKUP($D29&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I29" s="67" cm="1">
-        <f t="array" ref="I29">_xlfn.XLOOKUP($D29&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I29">_xlfn.XLOOKUP($D29&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J29" s="67" cm="1">
-        <f t="array" ref="J29">_xlfn.XLOOKUP($D29&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J29">_xlfn.XLOOKUP($D29&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K29" s="67" cm="1">
-        <f t="array" ref="K29">_xlfn.XLOOKUP($D29&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K29">_xlfn.XLOOKUP($D29&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L29" s="67" cm="1">
-        <f t="array" ref="L29">_xlfn.XLOOKUP($D29&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L29">_xlfn.XLOOKUP($D29&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M29" s="67" cm="1">
-        <f t="array" ref="M29">_xlfn.XLOOKUP($D29&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M29">_xlfn.XLOOKUP($D29&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N29" s="67" cm="1">
-        <f t="array" ref="N29">_xlfn.XLOOKUP($D29&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N29">_xlfn.XLOOKUP($D29&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O29" s="67" cm="1">
-        <f t="array" ref="O29">_xlfn.XLOOKUP($D29&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O29">_xlfn.XLOOKUP($D29&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P29" s="67" cm="1">
-        <f t="array" ref="P29">_xlfn.XLOOKUP($D29&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P29">_xlfn.XLOOKUP($D29&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q29" s="67" cm="1">
-        <f t="array" ref="Q29">_xlfn.XLOOKUP($D29&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q29">_xlfn.XLOOKUP($D29&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R29" s="67" cm="1">
-        <f t="array" ref="R29">_xlfn.XLOOKUP($D29&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R29">_xlfn.XLOOKUP($D29&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S29" s="67" cm="1">
-        <f t="array" ref="S29">_xlfn.XLOOKUP($D29&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S29">_xlfn.XLOOKUP($D29&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z29" s="5">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="2"/>
         <v>14</v>
       </c>
       <c r="AA29" s="2">
-        <f t="shared" ca="1" si="5"/>
-        <v>14</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>9999</v>
       </c>
       <c r="AB29">
         <f t="shared" si="23"/>
@@ -12105,67 +12057,67 @@
         <v>0</v>
       </c>
       <c r="AK29">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL29" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM29" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN29" s="1">
         <f t="shared" si="7"/>
-        <v>14</v>
-      </c>
-      <c r="AL29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="1">
         <f t="shared" si="8"/>
-        <v>14</v>
-      </c>
-      <c r="AM29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN29" s="1">
+      <c r="AQ29" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO29" s="1">
+      <c r="AR29" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP29" s="1">
+      <c r="AS29" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ29" s="1">
+      <c r="AT29" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR29" s="1">
+      <c r="AU29" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS29" s="1">
+      <c r="AV29" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT29" s="1">
+      <c r="AW29" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU29" s="1">
+      <c r="AX29" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV29" s="1">
+      <c r="AY29" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW29" s="1">
+      <c r="AZ29" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX29" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY29" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ29" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12174,83 +12126,83 @@
         <v>26</v>
       </c>
       <c r="B30" s="61">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="C30" s="56">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>31.2</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>48</v>
       </c>
       <c r="E30" s="67" cm="1">
-        <f t="array" ref="E30">_xlfn.XLOOKUP($D30&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>0</v>
+        <f t="array" ref="E30">_xlfn.XLOOKUP($D30&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>31.2</v>
       </c>
       <c r="F30" s="67" cm="1">
-        <f t="array" ref="F30">_xlfn.XLOOKUP($D30&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F30">_xlfn.XLOOKUP($D30&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G30" s="67" cm="1">
-        <f t="array" ref="G30">_xlfn.XLOOKUP($D30&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G30">_xlfn.XLOOKUP($D30&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H30" s="67" cm="1">
-        <f t="array" ref="H30">_xlfn.XLOOKUP($D30&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H30">_xlfn.XLOOKUP($D30&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I30" s="67" cm="1">
-        <f t="array" ref="I30">_xlfn.XLOOKUP($D30&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I30">_xlfn.XLOOKUP($D30&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J30" s="67" cm="1">
-        <f t="array" ref="J30">_xlfn.XLOOKUP($D30&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J30">_xlfn.XLOOKUP($D30&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K30" s="67" cm="1">
-        <f t="array" ref="K30">_xlfn.XLOOKUP($D30&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K30">_xlfn.XLOOKUP($D30&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L30" s="67" cm="1">
-        <f t="array" ref="L30">_xlfn.XLOOKUP($D30&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L30">_xlfn.XLOOKUP($D30&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M30" s="67" cm="1">
-        <f t="array" ref="M30">_xlfn.XLOOKUP($D30&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M30">_xlfn.XLOOKUP($D30&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N30" s="67" cm="1">
-        <f t="array" ref="N30">_xlfn.XLOOKUP($D30&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N30">_xlfn.XLOOKUP($D30&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O30" s="67" cm="1">
-        <f t="array" ref="O30">_xlfn.XLOOKUP($D30&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O30">_xlfn.XLOOKUP($D30&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P30" s="67" cm="1">
-        <f t="array" ref="P30">_xlfn.XLOOKUP($D30&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P30">_xlfn.XLOOKUP($D30&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q30" s="67" cm="1">
-        <f t="array" ref="Q30">_xlfn.XLOOKUP($D30&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q30">_xlfn.XLOOKUP($D30&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R30" s="67" cm="1">
-        <f t="array" ref="R30">_xlfn.XLOOKUP($D30&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R30">_xlfn.XLOOKUP($D30&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S30" s="67" cm="1">
-        <f t="array" ref="S30">_xlfn.XLOOKUP($D30&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S30">_xlfn.XLOOKUP($D30&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z30" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
       </c>
       <c r="AA30" s="2">
-        <f t="shared" ca="1" si="5"/>
-        <v>9999</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>5</v>
       </c>
       <c r="AB30">
         <f t="shared" si="23"/>
@@ -12289,67 +12241,67 @@
         <v>0</v>
       </c>
       <c r="AK30">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AL30" s="1">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AM30" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN30" s="1">
         <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="AL30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="1">
         <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="AM30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN30" s="1">
+      <c r="AQ30" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO30" s="1">
+      <c r="AR30" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP30" s="1">
+      <c r="AS30" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ30" s="1">
+      <c r="AT30" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR30" s="1">
+      <c r="AU30" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS30" s="1">
+      <c r="AV30" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT30" s="1">
+      <c r="AW30" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU30" s="1">
+      <c r="AX30" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV30" s="1">
+      <c r="AY30" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW30" s="1">
+      <c r="AZ30" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX30" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY30" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ30" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12358,83 +12310,83 @@
         <v>27</v>
       </c>
       <c r="B31" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="C31" s="56">
-        <f t="shared" si="3"/>
-        <v>31.1</v>
+        <f t="shared" si="21"/>
+        <v>30.96</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>34</v>
       </c>
       <c r="E31" s="67" cm="1">
-        <f t="array" ref="E31">_xlfn.XLOOKUP($D31&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>31.1</v>
+        <f t="array" ref="E31">_xlfn.XLOOKUP($D31&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>30.96</v>
       </c>
       <c r="F31" s="67" cm="1">
-        <f t="array" ref="F31">_xlfn.XLOOKUP($D31&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F31">_xlfn.XLOOKUP($D31&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G31" s="67" cm="1">
-        <f t="array" ref="G31">_xlfn.XLOOKUP($D31&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G31">_xlfn.XLOOKUP($D31&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H31" s="67" cm="1">
-        <f t="array" ref="H31">_xlfn.XLOOKUP($D31&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H31">_xlfn.XLOOKUP($D31&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I31" s="67" cm="1">
-        <f t="array" ref="I31">_xlfn.XLOOKUP($D31&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I31">_xlfn.XLOOKUP($D31&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J31" s="67" cm="1">
-        <f t="array" ref="J31">_xlfn.XLOOKUP($D31&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J31">_xlfn.XLOOKUP($D31&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K31" s="67" cm="1">
-        <f t="array" ref="K31">_xlfn.XLOOKUP($D31&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K31">_xlfn.XLOOKUP($D31&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L31" s="67" cm="1">
-        <f t="array" ref="L31">_xlfn.XLOOKUP($D31&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L31">_xlfn.XLOOKUP($D31&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M31" s="67" cm="1">
-        <f t="array" ref="M31">_xlfn.XLOOKUP($D31&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M31">_xlfn.XLOOKUP($D31&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N31" s="67" cm="1">
-        <f t="array" ref="N31">_xlfn.XLOOKUP($D31&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N31">_xlfn.XLOOKUP($D31&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O31" s="67" cm="1">
-        <f t="array" ref="O31">_xlfn.XLOOKUP($D31&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O31">_xlfn.XLOOKUP($D31&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P31" s="67" cm="1">
-        <f t="array" ref="P31">_xlfn.XLOOKUP($D31&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P31">_xlfn.XLOOKUP($D31&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q31" s="67" cm="1">
-        <f t="array" ref="Q31">_xlfn.XLOOKUP($D31&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q31">_xlfn.XLOOKUP($D31&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R31" s="67" cm="1">
-        <f t="array" ref="R31">_xlfn.XLOOKUP($D31&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R31">_xlfn.XLOOKUP($D31&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S31" s="67" cm="1">
-        <f t="array" ref="S31">_xlfn.XLOOKUP($D31&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S31">_xlfn.XLOOKUP($D31&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z31" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
       </c>
       <c r="AA31" s="2">
-        <f t="shared" ca="1" si="5"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>6</v>
       </c>
       <c r="AB31">
         <f t="shared" si="23"/>
@@ -12473,67 +12425,67 @@
         <v>0</v>
       </c>
       <c r="AK31">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="AL31" s="1">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="AM31" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN31" s="1">
         <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="AL31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="1">
         <f t="shared" si="8"/>
-        <v>3</v>
-      </c>
-      <c r="AM31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN31" s="1">
+      <c r="AQ31" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO31" s="1">
+      <c r="AR31" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP31" s="1">
+      <c r="AS31" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ31" s="1">
+      <c r="AT31" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR31" s="1">
+      <c r="AU31" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS31" s="1">
+      <c r="AV31" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT31" s="1">
+      <c r="AW31" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU31" s="1">
+      <c r="AX31" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV31" s="1">
+      <c r="AY31" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW31" s="1">
+      <c r="AZ31" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX31" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY31" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ31" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12542,82 +12494,82 @@
         <v>28</v>
       </c>
       <c r="B32" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="C32" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E32" s="67" cm="1">
-        <f t="array" ref="E32">_xlfn.XLOOKUP($D32&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="E32">_xlfn.XLOOKUP($D32&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="F32" s="67" cm="1">
-        <f t="array" ref="F32">_xlfn.XLOOKUP($D32&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F32">_xlfn.XLOOKUP($D32&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G32" s="67" cm="1">
-        <f t="array" ref="G32">_xlfn.XLOOKUP($D32&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G32">_xlfn.XLOOKUP($D32&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H32" s="67" cm="1">
-        <f t="array" ref="H32">_xlfn.XLOOKUP($D32&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H32">_xlfn.XLOOKUP($D32&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I32" s="67" cm="1">
-        <f t="array" ref="I32">_xlfn.XLOOKUP($D32&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I32">_xlfn.XLOOKUP($D32&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J32" s="67" cm="1">
-        <f t="array" ref="J32">_xlfn.XLOOKUP($D32&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J32">_xlfn.XLOOKUP($D32&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K32" s="67" cm="1">
-        <f t="array" ref="K32">_xlfn.XLOOKUP($D32&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K32">_xlfn.XLOOKUP($D32&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L32" s="67" cm="1">
-        <f t="array" ref="L32">_xlfn.XLOOKUP($D32&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L32">_xlfn.XLOOKUP($D32&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M32" s="67" cm="1">
-        <f t="array" ref="M32">_xlfn.XLOOKUP($D32&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M32">_xlfn.XLOOKUP($D32&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N32" s="67" cm="1">
-        <f t="array" ref="N32">_xlfn.XLOOKUP($D32&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N32">_xlfn.XLOOKUP($D32&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O32" s="67" cm="1">
-        <f t="array" ref="O32">_xlfn.XLOOKUP($D32&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O32">_xlfn.XLOOKUP($D32&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P32" s="67" cm="1">
-        <f t="array" ref="P32">_xlfn.XLOOKUP($D32&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P32">_xlfn.XLOOKUP($D32&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q32" s="67" cm="1">
-        <f t="array" ref="Q32">_xlfn.XLOOKUP($D32&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q32">_xlfn.XLOOKUP($D32&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R32" s="67" cm="1">
-        <f t="array" ref="R32">_xlfn.XLOOKUP($D32&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R32">_xlfn.XLOOKUP($D32&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S32" s="67" cm="1">
-        <f t="array" ref="S32">_xlfn.XLOOKUP($D32&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S32">_xlfn.XLOOKUP($D32&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z32" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="AA32" s="2">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="22"/>
         <v>9999</v>
       </c>
       <c r="AB32">
@@ -12657,67 +12609,67 @@
         <v>0</v>
       </c>
       <c r="AK32">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL32" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM32" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN32" s="1">
         <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="AL32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="1">
         <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="AM32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP32" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN32" s="1">
+      <c r="AQ32" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO32" s="1">
+      <c r="AR32" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP32" s="1">
+      <c r="AS32" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ32" s="1">
+      <c r="AT32" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR32" s="1">
+      <c r="AU32" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS32" s="1">
+      <c r="AV32" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT32" s="1">
+      <c r="AW32" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU32" s="1">
+      <c r="AX32" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV32" s="1">
+      <c r="AY32" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW32" s="1">
+      <c r="AZ32" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX32" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY32" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ32" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12726,83 +12678,83 @@
         <v>29</v>
       </c>
       <c r="B33" s="61">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="C33" s="56">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>32.44</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>75</v>
       </c>
       <c r="E33" s="67" cm="1">
-        <f t="array" ref="E33">_xlfn.XLOOKUP($D33&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>0</v>
+        <f t="array" ref="E33">_xlfn.XLOOKUP($D33&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>32.44</v>
       </c>
       <c r="F33" s="67" cm="1">
-        <f t="array" ref="F33">_xlfn.XLOOKUP($D33&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F33">_xlfn.XLOOKUP($D33&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G33" s="67" cm="1">
-        <f t="array" ref="G33">_xlfn.XLOOKUP($D33&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G33">_xlfn.XLOOKUP($D33&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H33" s="67" cm="1">
-        <f t="array" ref="H33">_xlfn.XLOOKUP($D33&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H33">_xlfn.XLOOKUP($D33&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I33" s="67" cm="1">
-        <f t="array" ref="I33">_xlfn.XLOOKUP($D33&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I33">_xlfn.XLOOKUP($D33&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J33" s="67" cm="1">
-        <f t="array" ref="J33">_xlfn.XLOOKUP($D33&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J33">_xlfn.XLOOKUP($D33&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K33" s="67" cm="1">
-        <f t="array" ref="K33">_xlfn.XLOOKUP($D33&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K33">_xlfn.XLOOKUP($D33&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L33" s="67" cm="1">
-        <f t="array" ref="L33">_xlfn.XLOOKUP($D33&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L33">_xlfn.XLOOKUP($D33&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M33" s="67" cm="1">
-        <f t="array" ref="M33">_xlfn.XLOOKUP($D33&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M33">_xlfn.XLOOKUP($D33&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N33" s="67" cm="1">
-        <f t="array" ref="N33">_xlfn.XLOOKUP($D33&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N33">_xlfn.XLOOKUP($D33&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O33" s="67" cm="1">
-        <f t="array" ref="O33">_xlfn.XLOOKUP($D33&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O33">_xlfn.XLOOKUP($D33&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P33" s="67" cm="1">
-        <f t="array" ref="P33">_xlfn.XLOOKUP($D33&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P33">_xlfn.XLOOKUP($D33&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q33" s="67" cm="1">
-        <f t="array" ref="Q33">_xlfn.XLOOKUP($D33&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q33">_xlfn.XLOOKUP($D33&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R33" s="67" cm="1">
-        <f t="array" ref="R33">_xlfn.XLOOKUP($D33&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R33">_xlfn.XLOOKUP($D33&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S33" s="67" cm="1">
-        <f t="array" ref="S33">_xlfn.XLOOKUP($D33&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S33">_xlfn.XLOOKUP($D33&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z33" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
       </c>
       <c r="AA33" s="2">
-        <f t="shared" ca="1" si="5"/>
-        <v>9999</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>3</v>
       </c>
       <c r="AB33">
         <f t="shared" si="23"/>
@@ -12841,67 +12793,67 @@
         <v>0</v>
       </c>
       <c r="AK33">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AL33" s="1">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AM33" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN33" s="1">
         <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="AL33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO33" s="1">
         <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="AM33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP33" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN33" s="1">
+      <c r="AQ33" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO33" s="1">
+      <c r="AR33" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP33" s="1">
+      <c r="AS33" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ33" s="1">
+      <c r="AT33" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR33" s="1">
+      <c r="AU33" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS33" s="1">
+      <c r="AV33" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT33" s="1">
+      <c r="AW33" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU33" s="1">
+      <c r="AX33" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV33" s="1">
+      <c r="AY33" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW33" s="1">
+      <c r="AZ33" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX33" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY33" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ33" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12910,83 +12862,83 @@
         <v>30</v>
       </c>
       <c r="B34" s="61">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="C34" s="56">
-        <f t="shared" si="3"/>
-        <v>30.05</v>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>37</v>
       </c>
       <c r="E34" s="67" cm="1">
-        <f t="array" ref="E34">_xlfn.XLOOKUP($D34&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
-        <v>30.05</v>
+        <f t="array" ref="E34">_xlfn.XLOOKUP($D34&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
+        <v>0</v>
       </c>
       <c r="F34" s="67" cm="1">
-        <f t="array" ref="F34">_xlfn.XLOOKUP($D34&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F34">_xlfn.XLOOKUP($D34&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G34" s="67" cm="1">
-        <f t="array" ref="G34">_xlfn.XLOOKUP($D34&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G34">_xlfn.XLOOKUP($D34&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H34" s="67" cm="1">
-        <f t="array" ref="H34">_xlfn.XLOOKUP($D34&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H34">_xlfn.XLOOKUP($D34&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I34" s="67" cm="1">
-        <f t="array" ref="I34">_xlfn.XLOOKUP($D34&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I34">_xlfn.XLOOKUP($D34&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J34" s="67" cm="1">
-        <f t="array" ref="J34">_xlfn.XLOOKUP($D34&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J34">_xlfn.XLOOKUP($D34&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K34" s="67" cm="1">
-        <f t="array" ref="K34">_xlfn.XLOOKUP($D34&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K34">_xlfn.XLOOKUP($D34&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L34" s="67" cm="1">
-        <f t="array" ref="L34">_xlfn.XLOOKUP($D34&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L34">_xlfn.XLOOKUP($D34&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M34" s="67" cm="1">
-        <f t="array" ref="M34">_xlfn.XLOOKUP($D34&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M34">_xlfn.XLOOKUP($D34&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N34" s="67" cm="1">
-        <f t="array" ref="N34">_xlfn.XLOOKUP($D34&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N34">_xlfn.XLOOKUP($D34&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O34" s="67" cm="1">
-        <f t="array" ref="O34">_xlfn.XLOOKUP($D34&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O34">_xlfn.XLOOKUP($D34&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P34" s="67" cm="1">
-        <f t="array" ref="P34">_xlfn.XLOOKUP($D34&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P34">_xlfn.XLOOKUP($D34&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q34" s="67" cm="1">
-        <f t="array" ref="Q34">_xlfn.XLOOKUP($D34&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q34">_xlfn.XLOOKUP($D34&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R34" s="67" cm="1">
-        <f t="array" ref="R34">_xlfn.XLOOKUP($D34&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R34">_xlfn.XLOOKUP($D34&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S34" s="67" cm="1">
-        <f t="array" ref="S34">_xlfn.XLOOKUP($D34&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S34">_xlfn.XLOOKUP($D34&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z34" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>5</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="AA34" s="2">
-        <f t="shared" ca="1" si="5"/>
-        <v>5</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>9999</v>
       </c>
       <c r="AB34">
         <f t="shared" si="23"/>
@@ -13025,67 +12977,67 @@
         <v>0</v>
       </c>
       <c r="AK34">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL34" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM34" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN34" s="1">
         <f t="shared" si="7"/>
-        <v>5</v>
-      </c>
-      <c r="AL34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="1">
         <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="AM34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN34" s="1">
+      <c r="AQ34" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO34" s="1">
+      <c r="AR34" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP34" s="1">
+      <c r="AS34" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ34" s="1">
+      <c r="AT34" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR34" s="1">
+      <c r="AU34" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS34" s="1">
+      <c r="AV34" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT34" s="1">
+      <c r="AW34" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU34" s="1">
+      <c r="AX34" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV34" s="1">
+      <c r="AY34" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW34" s="1">
+      <c r="AZ34" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX34" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY34" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ34" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -13094,82 +13046,82 @@
         <v>31</v>
       </c>
       <c r="B35" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="C35" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>68</v>
       </c>
       <c r="E35" s="67" cm="1">
-        <f t="array" ref="E35">_xlfn.XLOOKUP($D35&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="E35">_xlfn.XLOOKUP($D35&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="F35" s="67" cm="1">
-        <f t="array" ref="F35">_xlfn.XLOOKUP($D35&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F35">_xlfn.XLOOKUP($D35&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G35" s="67" cm="1">
-        <f t="array" ref="G35">_xlfn.XLOOKUP($D35&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G35">_xlfn.XLOOKUP($D35&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H35" s="67" cm="1">
-        <f t="array" ref="H35">_xlfn.XLOOKUP($D35&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H35">_xlfn.XLOOKUP($D35&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I35" s="67" cm="1">
-        <f t="array" ref="I35">_xlfn.XLOOKUP($D35&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I35">_xlfn.XLOOKUP($D35&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J35" s="67" cm="1">
-        <f t="array" ref="J35">_xlfn.XLOOKUP($D35&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J35">_xlfn.XLOOKUP($D35&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K35" s="67" cm="1">
-        <f t="array" ref="K35">_xlfn.XLOOKUP($D35&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K35">_xlfn.XLOOKUP($D35&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L35" s="67" cm="1">
-        <f t="array" ref="L35">_xlfn.XLOOKUP($D35&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L35">_xlfn.XLOOKUP($D35&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M35" s="67" cm="1">
-        <f t="array" ref="M35">_xlfn.XLOOKUP($D35&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M35">_xlfn.XLOOKUP($D35&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N35" s="67" cm="1">
-        <f t="array" ref="N35">_xlfn.XLOOKUP($D35&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N35">_xlfn.XLOOKUP($D35&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O35" s="67" cm="1">
-        <f t="array" ref="O35">_xlfn.XLOOKUP($D35&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O35">_xlfn.XLOOKUP($D35&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P35" s="67" cm="1">
-        <f t="array" ref="P35">_xlfn.XLOOKUP($D35&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P35">_xlfn.XLOOKUP($D35&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q35" s="67" cm="1">
-        <f t="array" ref="Q35">_xlfn.XLOOKUP($D35&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q35">_xlfn.XLOOKUP($D35&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R35" s="67" cm="1">
-        <f t="array" ref="R35">_xlfn.XLOOKUP($D35&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R35">_xlfn.XLOOKUP($D35&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S35" s="67" cm="1">
-        <f t="array" ref="S35">_xlfn.XLOOKUP($D35&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S35">_xlfn.XLOOKUP($D35&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z35" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="AA35" s="2">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="22"/>
         <v>9999</v>
       </c>
       <c r="AB35">
@@ -13209,67 +13161,67 @@
         <v>0</v>
       </c>
       <c r="AK35">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL35" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM35" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN35" s="1">
         <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="AL35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO35" s="1">
         <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="AM35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP35" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN35" s="1">
+      <c r="AQ35" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO35" s="1">
+      <c r="AR35" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP35" s="1">
+      <c r="AS35" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ35" s="1">
+      <c r="AT35" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR35" s="1">
+      <c r="AU35" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS35" s="1">
+      <c r="AV35" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT35" s="1">
+      <c r="AW35" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU35" s="1">
+      <c r="AX35" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV35" s="1">
+      <c r="AY35" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW35" s="1">
+      <c r="AZ35" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX35" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY35" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ35" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -13278,82 +13230,82 @@
         <v>32</v>
       </c>
       <c r="B36" s="61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="C36" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D36" s="57" t="s">
         <v>85</v>
       </c>
       <c r="E36" s="67" cm="1">
-        <f t="array" ref="E36">_xlfn.XLOOKUP($D36&amp;E$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="E36">_xlfn.XLOOKUP($D36&amp;E$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="F36" s="67" cm="1">
-        <f t="array" ref="F36">_xlfn.XLOOKUP($D36&amp;F$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="F36">_xlfn.XLOOKUP($D36&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="G36" s="67" cm="1">
-        <f t="array" ref="G36">_xlfn.XLOOKUP($D36&amp;G$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="G36">_xlfn.XLOOKUP($D36&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="H36" s="67" cm="1">
-        <f t="array" ref="H36">_xlfn.XLOOKUP($D36&amp;H$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="H36">_xlfn.XLOOKUP($D36&amp;H$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="I36" s="67" cm="1">
-        <f t="array" ref="I36">_xlfn.XLOOKUP($D36&amp;I$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="I36">_xlfn.XLOOKUP($D36&amp;I$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="J36" s="67" cm="1">
-        <f t="array" ref="J36">_xlfn.XLOOKUP($D36&amp;J$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="J36">_xlfn.XLOOKUP($D36&amp;J$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="K36" s="67" cm="1">
-        <f t="array" ref="K36">_xlfn.XLOOKUP($D36&amp;K$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="K36">_xlfn.XLOOKUP($D36&amp;K$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="L36" s="67" cm="1">
-        <f t="array" ref="L36">_xlfn.XLOOKUP($D36&amp;L$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="L36">_xlfn.XLOOKUP($D36&amp;L$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="M36" s="67" cm="1">
-        <f t="array" ref="M36">_xlfn.XLOOKUP($D36&amp;M$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="M36">_xlfn.XLOOKUP($D36&amp;M$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="N36" s="67" cm="1">
-        <f t="array" ref="N36">_xlfn.XLOOKUP($D36&amp;N$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="N36">_xlfn.XLOOKUP($D36&amp;N$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="O36" s="67" cm="1">
-        <f t="array" ref="O36">_xlfn.XLOOKUP($D36&amp;O$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="O36">_xlfn.XLOOKUP($D36&amp;O$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="P36" s="67" cm="1">
-        <f t="array" ref="P36">_xlfn.XLOOKUP($D36&amp;P$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="P36">_xlfn.XLOOKUP($D36&amp;P$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Q36" s="67" cm="1">
-        <f t="array" ref="Q36">_xlfn.XLOOKUP($D36&amp;Q$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="Q36">_xlfn.XLOOKUP($D36&amp;Q$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="R36" s="67" cm="1">
-        <f t="array" ref="R36">_xlfn.XLOOKUP($D36&amp;R$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="R36">_xlfn.XLOOKUP($D36&amp;R$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="S36" s="67" cm="1">
-        <f t="array" ref="S36">_xlfn.XLOOKUP($D36&amp;S$1,Results_of_the_day!$C:$C&amp;Results_of_the_day!$B:$B,Results_of_the_day!$D:$D,0,0)</f>
+        <f t="array" ref="S36">_xlfn.XLOOKUP($D36&amp;S$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
         <v>0</v>
       </c>
       <c r="Z36" s="5">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="AA36" s="2">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="22"/>
         <v>9999</v>
       </c>
       <c r="AB36">
@@ -13393,67 +13345,67 @@
         <v>0</v>
       </c>
       <c r="AK36">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AL36" s="1">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="AM36" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN36" s="1">
         <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="AL36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="1">
         <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="AM36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP36" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN36" s="1">
+      <c r="AQ36" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO36" s="1">
+      <c r="AR36" s="1">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP36" s="1">
+      <c r="AS36" s="1">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AQ36" s="1">
+      <c r="AT36" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AR36" s="1">
+      <c r="AU36" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AS36" s="1">
+      <c r="AV36" s="1">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT36" s="1">
+      <c r="AW36" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AU36" s="1">
+      <c r="AX36" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AV36" s="1">
+      <c r="AY36" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AW36" s="1">
+      <c r="AZ36" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AX36" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AY36" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AZ36" s="1">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -13471,7 +13423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8DDE8D9-5BFB-446D-8B12-DC8087DAB60A}">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:AB51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.5703125" customWidth="1"/>
@@ -13482,7 +13434,7 @@
     <col min="7" max="7" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="52.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="52.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="68" t="s">
         <v>69</v>
       </c>
@@ -13490,614 +13442,581 @@
         <v>78</v>
       </c>
       <c r="C1" s="68" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D1" s="68" t="s">
         <v>71</v>
       </c>
       <c r="E1" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" s="68" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="F1" s="68" t="s">
+      <c r="H1" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="G1" s="68" t="s">
+      <c r="I1" s="68" t="s">
         <v>105</v>
-      </c>
-      <c r="H1" s="68" t="s">
-        <v>106</v>
-      </c>
-      <c r="I1" s="68" t="s">
-        <v>107</v>
       </c>
       <c r="J1" s="68" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="23">
-        <v>45802</v>
+        <v>46137</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D2">
-        <v>34.75</v>
+        <v>33.869999999999997</v>
       </c>
       <c r="E2">
-        <v>36.35</v>
+        <v>36.36</v>
       </c>
       <c r="F2">
-        <v>33.130000000000003</v>
+        <v>31.59</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H2">
-        <v>10.43</v>
+        <v>10.79</v>
       </c>
       <c r="I2">
-        <v>40.4</v>
+        <v>50.86</v>
       </c>
       <c r="J2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>15.95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="23">
-        <v>45802</v>
+        <v>46137</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="D3">
-        <v>31.2</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="E3">
-        <v>32.76</v>
+        <v>35.42</v>
       </c>
       <c r="F3">
-        <v>30.27</v>
+        <v>30.28</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>21.62</v>
       </c>
       <c r="H3">
-        <v>6.74</v>
+        <v>5.99</v>
       </c>
       <c r="I3">
-        <v>37.97</v>
+        <v>17.55</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="23">
-        <v>45802</v>
+        <v>46137</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D4">
-        <v>31.1</v>
+        <v>32.44</v>
       </c>
       <c r="E4">
-        <v>34.200000000000003</v>
+        <v>35.229999999999997</v>
       </c>
       <c r="F4">
-        <v>27.2</v>
+        <v>30.61</v>
       </c>
       <c r="G4">
-        <v>23.39</v>
+        <v>20.16</v>
       </c>
       <c r="H4">
-        <v>16.059999999999999</v>
+        <v>11.07</v>
       </c>
       <c r="I4">
-        <v>89.29</v>
+        <v>21.14</v>
       </c>
       <c r="J4">
-        <v>20.81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>15.57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="23">
-        <v>45802</v>
+        <v>46137</v>
       </c>
       <c r="C5" t="s">
         <v>36</v>
       </c>
       <c r="D5">
-        <v>31.01</v>
+        <v>31.32</v>
       </c>
       <c r="E5">
-        <v>32.409999999999997</v>
+        <v>33.69</v>
       </c>
       <c r="F5">
-        <v>30.84</v>
+        <v>28.12</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>12.84</v>
+        <v>11.85</v>
       </c>
       <c r="I5">
-        <v>51.2</v>
+        <v>21.95</v>
       </c>
       <c r="J5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>13.28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="23">
-        <v>45802</v>
+        <v>46137</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D6">
-        <v>30.05</v>
+        <v>31.2</v>
       </c>
       <c r="E6">
-        <v>33.700000000000003</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>28.33</v>
+        <v>28.54</v>
       </c>
       <c r="G6">
-        <v>24.77</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>13.37</v>
+        <v>14.69</v>
       </c>
       <c r="I6">
-        <v>65.63</v>
+        <v>53.7</v>
       </c>
       <c r="J6">
-        <v>19.690000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>17.32</v>
+      </c>
+      <c r="S6">
+        <v>14</v>
+      </c>
+      <c r="T6" s="23">
+        <v>46137</v>
+      </c>
+      <c r="U6" t="s">
+        <v>42</v>
+      </c>
+      <c r="V6">
+        <v>24.46</v>
+      </c>
+      <c r="W6">
+        <v>26.9</v>
+      </c>
+      <c r="X6">
+        <v>24.05</v>
+      </c>
+      <c r="Y6">
+        <v>20.53</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>11.3</v>
+      </c>
+      <c r="AB6">
+        <v>17.82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="23">
-        <v>45802</v>
+        <v>46137</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7">
-        <v>29.71</v>
+        <v>30.96</v>
       </c>
       <c r="E7">
-        <v>31.57</v>
+        <v>33.369999999999997</v>
       </c>
       <c r="F7">
-        <v>28.69</v>
+        <v>28.32</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>23.55</v>
       </c>
       <c r="H7">
-        <v>8.9499999999999993</v>
+        <v>13.77</v>
       </c>
       <c r="I7">
-        <v>43.87</v>
+        <v>26.3</v>
       </c>
       <c r="J7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>22.07</v>
+      </c>
+      <c r="S7">
+        <v>15</v>
+      </c>
+      <c r="T7" s="23">
+        <v>46137</v>
+      </c>
+      <c r="U7" t="s">
+        <v>42</v>
+      </c>
+      <c r="V7">
+        <v>24.05</v>
+      </c>
+      <c r="W7">
+        <v>26.3</v>
+      </c>
+      <c r="X7">
+        <v>23.8</v>
+      </c>
+      <c r="Y7">
+        <v>20.48</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>7.76</v>
+      </c>
+      <c r="AB7">
+        <v>17.16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="23">
-        <v>45802</v>
+        <v>46137</v>
       </c>
       <c r="C8" t="s">
         <v>40</v>
       </c>
       <c r="D8">
-        <v>29.7</v>
+        <v>30.39</v>
       </c>
       <c r="E8">
-        <v>31.05</v>
+        <v>32</v>
       </c>
       <c r="F8">
-        <v>27.39</v>
+        <v>29.61</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>20.52</v>
       </c>
       <c r="H8">
-        <v>8.4</v>
+        <v>11.49</v>
       </c>
       <c r="I8">
-        <v>45.14</v>
+        <v>40.28</v>
       </c>
       <c r="J8">
-        <v>8.52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>15.93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="23">
-        <v>45802</v>
+        <v>46137</v>
       </c>
       <c r="C9" t="s">
         <v>50</v>
       </c>
       <c r="D9">
-        <v>29.41</v>
+        <v>30.09</v>
       </c>
       <c r="E9">
-        <v>30.6</v>
+        <v>32.01</v>
       </c>
       <c r="F9">
         <v>27.97</v>
       </c>
       <c r="G9">
-        <v>18.899999999999999</v>
+        <v>17.77</v>
       </c>
       <c r="H9">
-        <v>8.2899999999999991</v>
+        <v>8.9</v>
       </c>
       <c r="I9">
-        <v>37.69</v>
+        <v>38.93</v>
       </c>
       <c r="J9">
-        <v>15.38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>13.88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="23">
-        <v>45802</v>
+        <v>46137</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="D10">
+        <v>30.01</v>
+      </c>
+      <c r="E10">
+        <v>32.049999999999997</v>
+      </c>
+      <c r="F10">
         <v>29.12</v>
       </c>
-      <c r="E10">
-        <v>30.3</v>
-      </c>
-      <c r="F10">
-        <v>28.16</v>
-      </c>
       <c r="G10">
-        <v>21.41</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>16.399999999999999</v>
+        <v>10.18</v>
       </c>
       <c r="I10">
-        <v>104.49</v>
+        <v>26.46</v>
       </c>
       <c r="J10">
-        <v>18.11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="23">
-        <v>45802</v>
+        <v>46137</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="D11">
-        <v>28.9</v>
+        <v>29.73</v>
       </c>
       <c r="E11">
-        <v>29.4</v>
+        <v>31.36</v>
       </c>
       <c r="F11">
-        <v>28.4</v>
+        <v>30.01</v>
       </c>
       <c r="G11">
-        <v>19.73</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>12.52</v>
+        <v>9.4600000000000009</v>
       </c>
       <c r="I11">
-        <v>63.31</v>
+        <v>27.48</v>
       </c>
       <c r="J11">
-        <v>14.29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19.41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="23">
-        <v>45802</v>
+        <v>46137</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D12">
-        <v>28.34</v>
+        <v>28.02</v>
       </c>
       <c r="E12">
-        <v>29.97</v>
+        <v>29.35</v>
       </c>
       <c r="F12">
-        <v>27.31</v>
+        <v>26.84</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>21.09</v>
       </c>
       <c r="H12">
-        <v>9.7799999999999994</v>
+        <v>12.43</v>
       </c>
       <c r="I12">
-        <v>47.36</v>
+        <v>31.6</v>
       </c>
       <c r="J12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>15.71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="23">
-        <v>45802</v>
+        <v>46137</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D13">
-        <v>27.73</v>
+        <v>27.02</v>
       </c>
       <c r="E13">
-        <v>29.3</v>
+        <v>28.6</v>
       </c>
       <c r="F13">
-        <v>26.12</v>
+        <v>25.72</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>21.37</v>
       </c>
       <c r="H13">
-        <v>10.1</v>
+        <v>12.61</v>
       </c>
       <c r="I13">
-        <v>22.03</v>
+        <v>25.52</v>
       </c>
       <c r="J13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>16.420000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="23">
-        <v>45802</v>
+        <v>46137</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D14">
-        <v>26.47</v>
+        <v>25.22</v>
       </c>
       <c r="E14">
-        <v>27.3</v>
+        <v>26.6</v>
       </c>
       <c r="F14">
-        <v>25.58</v>
+        <v>25.23</v>
       </c>
       <c r="G14">
-        <v>19.579999999999998</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>10.25</v>
+        <v>5.57</v>
       </c>
       <c r="I14">
-        <v>33.68</v>
+        <v>10.38</v>
       </c>
       <c r="J14">
-        <v>14.44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" s="23">
-        <v>45802</v>
+        <v>46137</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="D15">
-        <v>25.93</v>
+        <v>24.02</v>
       </c>
       <c r="E15">
-        <v>27.03</v>
+        <v>26.2</v>
       </c>
       <c r="F15">
-        <v>25.01</v>
+        <v>22.58</v>
       </c>
       <c r="G15">
-        <v>18.39</v>
+        <v>19.670000000000002</v>
       </c>
       <c r="H15">
-        <v>10.54</v>
+        <v>12.56</v>
       </c>
       <c r="I15">
-        <v>25.41</v>
+        <v>30.49</v>
       </c>
       <c r="J15">
-        <v>16.170000000000002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" s="23">
-        <v>45802</v>
-      </c>
-      <c r="C16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16">
-        <v>25.4</v>
-      </c>
-      <c r="E16">
-        <v>27.1</v>
-      </c>
-      <c r="F16">
-        <v>24.42</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>5.42</v>
-      </c>
-      <c r="I16">
-        <v>14.33</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" s="23">
-        <v>45802</v>
-      </c>
-      <c r="C17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17">
-        <v>25.11</v>
-      </c>
-      <c r="E17">
-        <v>26.56</v>
-      </c>
-      <c r="F17">
-        <v>23.83</v>
-      </c>
-      <c r="G17">
-        <v>16.920000000000002</v>
-      </c>
-      <c r="H17">
-        <v>12.51</v>
-      </c>
-      <c r="I17">
-        <v>24.02</v>
-      </c>
-      <c r="J17">
-        <v>15.25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" s="23">
-        <v>45802</v>
-      </c>
-      <c r="C18" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18">
-        <v>20.3</v>
-      </c>
-      <c r="E18">
-        <v>22.34</v>
-      </c>
-      <c r="F18">
-        <v>18.61</v>
-      </c>
-      <c r="G18">
-        <v>13.5</v>
-      </c>
-      <c r="H18">
-        <v>10.11</v>
-      </c>
-      <c r="I18">
-        <v>20.56</v>
-      </c>
-      <c r="J18">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>17.41</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="23"/>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="23"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="23"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="23"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="23"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="23"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="23"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" s="23"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="23"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="23"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="23"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="23"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" s="23"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" s="23"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" s="23"/>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
@@ -14156,69 +14075,6 @@
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" s="23"/>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B52" s="23"/>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B53" s="23"/>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B54" s="23"/>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B55" s="23"/>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B56" s="23"/>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B57" s="23"/>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B58" s="23"/>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B59" s="23"/>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B60" s="23"/>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B61" s="23"/>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B62" s="23"/>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B63" s="23"/>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B64" s="23"/>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B65" s="23"/>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B66" s="23"/>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B67" s="23"/>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B68" s="23"/>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B69" s="23"/>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B70" s="23"/>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B71" s="23"/>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B72" s="23"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{E8DDE8D9-5BFB-446D-8B12-DC8087DAB60A}">

--- a/KoF/2026_KoF_Resutl.xlsx
+++ b/KoF/2026_KoF_Resutl.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F32CA77-6C49-447A-9715-F9D443BB3384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7C2BDA-099E-4C1C-AC9E-A4F4FE210939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{521ED91F-5C26-4B0E-8403-9E93154C70E8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{521ED91F-5C26-4B0E-8403-9E93154C70E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Guide" sheetId="9" r:id="rId1"/>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1267,37 +1267,19 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="13" fillId="7" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="13" fillId="7" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="13" fillId="7" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="13" fillId="7" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="13" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1310,6 +1292,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="13" fillId="7" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="7" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="7" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="7" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2454,15 +2454,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="17" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
       <c r="I1" s="24"/>
       <c r="J1" s="16"/>
       <c r="K1" s="24"/>
@@ -2488,120 +2488,120 @@
     <row r="2" spans="1:33" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
-      <c r="D2" s="73">
+      <c r="D2" s="69">
         <v>1</v>
       </c>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73">
+      <c r="E2" s="69"/>
+      <c r="F2" s="69">
         <v>2</v>
       </c>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73">
+      <c r="G2" s="69"/>
+      <c r="H2" s="69">
         <v>3</v>
       </c>
-      <c r="I2" s="73"/>
-      <c r="J2" s="74">
+      <c r="I2" s="69"/>
+      <c r="J2" s="80">
         <v>4</v>
       </c>
-      <c r="K2" s="74"/>
-      <c r="L2" s="73">
+      <c r="K2" s="80"/>
+      <c r="L2" s="69">
         <v>5</v>
       </c>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73">
+      <c r="M2" s="69"/>
+      <c r="N2" s="69">
         <v>6</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73">
+      <c r="O2" s="69"/>
+      <c r="P2" s="69">
         <v>7</v>
       </c>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73">
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69">
         <v>8</v>
       </c>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73">
+      <c r="S2" s="69"/>
+      <c r="T2" s="69">
         <v>9</v>
       </c>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73">
+      <c r="U2" s="69"/>
+      <c r="V2" s="69">
         <v>10</v>
       </c>
-      <c r="W2" s="73"/>
-      <c r="X2" s="73">
+      <c r="W2" s="69"/>
+      <c r="X2" s="69">
         <v>11</v>
       </c>
-      <c r="Y2" s="73"/>
-      <c r="Z2" s="73">
+      <c r="Y2" s="69"/>
+      <c r="Z2" s="69">
         <v>12</v>
       </c>
-      <c r="AA2" s="73"/>
-      <c r="AB2" s="73">
+      <c r="AA2" s="69"/>
+      <c r="AB2" s="69">
         <v>13</v>
       </c>
-      <c r="AC2" s="73"/>
-      <c r="AD2" s="73">
+      <c r="AC2" s="69"/>
+      <c r="AD2" s="69">
         <v>14</v>
       </c>
-      <c r="AE2" s="73"/>
-      <c r="AF2" s="73">
+      <c r="AE2" s="69"/>
+      <c r="AF2" s="69">
         <v>15</v>
       </c>
-      <c r="AG2" s="73"/>
+      <c r="AG2" s="69"/>
     </row>
     <row r="3" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="71" t="s">
+      <c r="A3" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="71" t="s">
+      <c r="C3" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="80">
+      <c r="D3" s="74">
         <v>45802</v>
       </c>
-      <c r="E3" s="80"/>
-      <c r="F3" s="81">
+      <c r="E3" s="74"/>
+      <c r="F3" s="75">
         <v>45815</v>
       </c>
-      <c r="G3" s="81"/>
-      <c r="H3" s="82">
+      <c r="G3" s="75"/>
+      <c r="H3" s="76">
         <v>45817</v>
       </c>
-      <c r="I3" s="83"/>
-      <c r="J3" s="75">
+      <c r="I3" s="77"/>
+      <c r="J3" s="81">
         <v>45837</v>
       </c>
-      <c r="K3" s="76"/>
-      <c r="L3" s="77"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="78"/>
-      <c r="R3" s="78"/>
-      <c r="S3" s="78"/>
-      <c r="T3" s="78"/>
-      <c r="U3" s="78"/>
-      <c r="V3" s="78"/>
-      <c r="W3" s="78"/>
-      <c r="X3" s="78"/>
-      <c r="Y3" s="78"/>
-      <c r="Z3" s="78"/>
-      <c r="AA3" s="78"/>
-      <c r="AB3" s="78"/>
-      <c r="AC3" s="78"/>
-      <c r="AD3" s="78"/>
-      <c r="AE3" s="78"/>
-      <c r="AF3" s="78"/>
-      <c r="AG3" s="78"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="70"/>
+      <c r="N3" s="70"/>
+      <c r="O3" s="70"/>
+      <c r="P3" s="70"/>
+      <c r="Q3" s="70"/>
+      <c r="R3" s="70"/>
+      <c r="S3" s="70"/>
+      <c r="T3" s="70"/>
+      <c r="U3" s="70"/>
+      <c r="V3" s="70"/>
+      <c r="W3" s="70"/>
+      <c r="X3" s="70"/>
+      <c r="Y3" s="70"/>
+      <c r="Z3" s="70"/>
+      <c r="AA3" s="70"/>
+      <c r="AB3" s="70"/>
+      <c r="AC3" s="70"/>
+      <c r="AD3" s="70"/>
+      <c r="AE3" s="70"/>
+      <c r="AF3" s="70"/>
+      <c r="AG3" s="70"/>
     </row>
     <row r="4" spans="1:33" s="20" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A4" s="70"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
+      <c r="A4" s="79"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
       <c r="D4" s="31" t="s">
         <v>86</v>
       </c>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="C5" s="40">
         <f ca="1">_xlfn.XLOOKUP($B5,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="28">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B5,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
@@ -2715,11 +2715,11 @@
       </c>
       <c r="F5" s="28">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B5,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B5,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>33.869999999999997</v>
       </c>
       <c r="H5" s="28">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B5,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,H$2-1)</f>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="C6" s="40">
         <f ca="1">_xlfn.XLOOKUP($B6,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B6,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
@@ -2848,11 +2848,11 @@
       </c>
       <c r="F6" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B6,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B6,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="H6" s="28">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B6,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,H$2-1)</f>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="C7" s="40">
         <f ca="1">_xlfn.XLOOKUP($B7,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D7" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B7,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
@@ -2981,11 +2981,11 @@
       </c>
       <c r="F7" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B7,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B7,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>32.44</v>
       </c>
       <c r="H7" s="28">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B7,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,H$2-1)</f>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="C8" s="40">
         <f ca="1">_xlfn.XLOOKUP($B8,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D8" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B8,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
@@ -3114,11 +3114,11 @@
       </c>
       <c r="F8" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B8,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G8" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B8,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>31.32</v>
       </c>
       <c r="H8" s="28">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B8,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,H$2-1)</f>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="C9" s="40">
         <f ca="1">_xlfn.XLOOKUP($B9,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D9" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B9,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
@@ -3247,11 +3247,11 @@
       </c>
       <c r="F9" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B9,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G9" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B9,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="H9" s="28">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B9,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,H$2-1)</f>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="C10" s="40">
         <f ca="1">_xlfn.XLOOKUP($B10,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D10" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B10,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
@@ -3380,11 +3380,11 @@
       </c>
       <c r="F10" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B10,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G10" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B10,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>30.96</v>
       </c>
       <c r="H10" s="28">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B10,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,H$2-1)</f>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="C11" s="40">
         <f ca="1">_xlfn.XLOOKUP($B11,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D11" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B11,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
@@ -3513,11 +3513,11 @@
       </c>
       <c r="F11" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B11,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G11" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B11,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>30.39</v>
       </c>
       <c r="H11" s="28">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B11,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,H$2-1)</f>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="C12" s="40">
         <f ca="1">_xlfn.XLOOKUP($B12,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D12" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B12,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
@@ -3646,11 +3646,11 @@
       </c>
       <c r="F12" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B12,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G12" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B12,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>30.09</v>
       </c>
       <c r="H12" s="28">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B12,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,H$2-1)</f>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="C13" s="40">
         <f ca="1">_xlfn.XLOOKUP($B13,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D13" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B13,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
@@ -3779,11 +3779,11 @@
       </c>
       <c r="F13" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B13,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G13" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B13,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>30.01</v>
       </c>
       <c r="H13" s="28">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B13,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,H$2-1)</f>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="C14" s="40">
         <f ca="1">_xlfn.XLOOKUP($B14,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D14" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B14,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
@@ -3912,11 +3912,11 @@
       </c>
       <c r="F14" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B14,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G14" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B14,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>28.02</v>
       </c>
       <c r="H14" s="28">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B14,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,H$2-1)</f>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="C15" s="40">
         <f ca="1">_xlfn.XLOOKUP($B15,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D15" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B15,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
@@ -4045,11 +4045,11 @@
       </c>
       <c r="F15" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B15,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G15" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B15,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>27.02</v>
       </c>
       <c r="H15" s="28">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B15,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,H$2-1)</f>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="C16" s="40">
         <f ca="1">_xlfn.XLOOKUP($B16,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D16" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B16,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
@@ -4178,11 +4178,11 @@
       </c>
       <c r="F16" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B16,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G16" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B16,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>25.22</v>
       </c>
       <c r="H16" s="28">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B16,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,H$2-1)</f>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C17" s="40">
         <f ca="1">_xlfn.XLOOKUP($B17,Resultat!$D:$D,Resultat!$AA:$AA,-1,0)</f>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D17" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B17,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,D$2-1)</f>
@@ -4311,11 +4311,11 @@
       </c>
       <c r="F17" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B17,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G17" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B17,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>24.02</v>
       </c>
       <c r="H17" s="28">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B17,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,H$2-1)</f>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="F18" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B18,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G18" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B18,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="F19" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B19,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G19" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B19,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="F20" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B20,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G20" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B20,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="F21" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B21,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G21" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B21,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="F22" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B22,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G22" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B22,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="F23" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B23,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G23" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B23,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="F24" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B24,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G24" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B24,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="F25" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B25,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G25" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B25,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="F26" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B26,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G26" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B26,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="F27" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B27,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G27" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B27,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F28" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B28,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G28" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B28,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="F29" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B29,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G29" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B29,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="F30" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B30,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G30" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B30,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="F31" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B31,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G31" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B31,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="F32" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B32,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G32" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B32,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="F33" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B33,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G33" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B33,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="F34" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B34,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G34" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B34,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="F35" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B35,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G35" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B35,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="F36" s="25">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B36,Resultat!$D:$D,Resultat!$AL:$AL,-1,0),0,F$2-1)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G36" s="29">
         <f ca="1">OFFSET(_xlfn.XLOOKUP($B36,Resultat!$D:$D,Resultat!$E:$E,-1,0),0,F$2-1)</f>
@@ -7100,6 +7100,25 @@
     <sortCondition ref="B39:B89"/>
   </sortState>
   <mergeCells count="34">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
     <mergeCell ref="AD2:AE2"/>
     <mergeCell ref="AD3:AE3"/>
     <mergeCell ref="AF2:AG2"/>
@@ -7115,25 +7134,6 @@
     <mergeCell ref="X3:Y3"/>
     <mergeCell ref="Z3:AA3"/>
     <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="N3:O3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:AG36">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -7176,7 +7176,9 @@
       <c r="E1" s="53">
         <v>46137</v>
       </c>
-      <c r="F1" s="53"/>
+      <c r="F1" s="53">
+        <v>46137</v>
+      </c>
       <c r="G1" s="53"/>
       <c r="H1" s="53"/>
       <c r="I1" s="54"/>
@@ -7194,7 +7196,7 @@
     <row r="2" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
         <f>SUM(E2:X2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="59">
         <f>VLOOKUP(A2,Regler!A2:B30,2)</f>
@@ -7206,7 +7208,7 @@
       </c>
       <c r="F2" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="6">
         <f t="shared" si="0"/>
@@ -7266,7 +7268,7 @@
       </c>
       <c r="AM2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN2">
         <f t="shared" si="1"/>
@@ -7542,7 +7544,7 @@
       </c>
       <c r="F5" s="67" cm="1">
         <f t="array" ref="F5">_xlfn.XLOOKUP($D5&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
-        <v>0</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="G5" s="67" cm="1">
         <f t="array" ref="G5">_xlfn.XLOOKUP($D5&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
@@ -7602,7 +7604,7 @@
       </c>
       <c r="AA5" s="2">
         <f ca="1">IF($B5,OFFSET(AK5,0,-$B$2),9999)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB5">
         <f t="shared" ref="AB5:AJ5" si="3">AC5-LARGE($AL5:$AZ5,AB$3)</f>
@@ -7638,11 +7640,11 @@
       </c>
       <c r="AJ5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK5">
         <f t="shared" ref="AK5:AK36" si="4">SUM(AL5:AZ5)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL5" s="1">
         <f t="shared" ref="AL5:AL36" si="5">IF(E5&gt;0,_xlfn.RANK.EQ(E5,E$5:E$36,0),$A$3+1)*AL$2</f>
@@ -7650,7 +7652,7 @@
       </c>
       <c r="AM5" s="1">
         <f t="shared" ref="AM5:AM36" si="6">IF(F5&gt;0,_xlfn.RANK.EQ(F5,F$5:F$36,0),$A$3+1)*AM$2</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN5" s="1">
         <f t="shared" ref="AN5:AN36" si="7">IF(G5&gt;0,_xlfn.RANK.EQ(G5,G$5:G$36,0),$A$3+1)*AN$2</f>
@@ -7710,11 +7712,11 @@
         <v>2</v>
       </c>
       <c r="B6" s="61">
-        <f t="shared" ref="B5:B36" si="20">IF(C6&gt;0,1,0)</f>
+        <f t="shared" ref="B6:B36" si="20">IF(C6&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="C6" s="56">
-        <f t="shared" ref="C5:C36" si="21">SUM($E6:$S6)/$A$2</f>
+        <f t="shared" ref="C6:C36" si="21">SUM($E6:$S6)/$A$2</f>
         <v>0</v>
       </c>
       <c r="D6" s="9" t="s">
@@ -7785,7 +7787,7 @@
         <v>14</v>
       </c>
       <c r="AA6" s="2">
-        <f t="shared" ref="AA5:AA36" ca="1" si="22">IF($B6,OFFSET(AK6,0,-$B$2),9999)</f>
+        <f t="shared" ref="AA6:AA36" ca="1" si="22">IF($B6,OFFSET(AK6,0,-$B$2),9999)</f>
         <v>9999</v>
       </c>
       <c r="AB6">
@@ -7822,11 +7824,11 @@
       </c>
       <c r="AJ6">
         <f t="shared" ref="AJ6:AJ36" si="28">AK6-LARGE($AL6:$AZ6,AJ$3)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK6">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL6" s="1">
         <f t="shared" si="5"/>
@@ -7834,7 +7836,7 @@
       </c>
       <c r="AM6" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN6" s="1">
         <f t="shared" si="7"/>
@@ -7910,7 +7912,7 @@
       </c>
       <c r="F7" s="67" cm="1">
         <f t="array" ref="F7">_xlfn.XLOOKUP($D7&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
-        <v>0</v>
+        <v>28.02</v>
       </c>
       <c r="G7" s="67" cm="1">
         <f t="array" ref="G7">_xlfn.XLOOKUP($D7&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
@@ -7970,7 +7972,7 @@
       </c>
       <c r="AA7" s="2">
         <f t="shared" ca="1" si="22"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB7">
         <f t="shared" si="23"/>
@@ -8006,11 +8008,11 @@
       </c>
       <c r="AJ7">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AK7">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AL7" s="1">
         <f t="shared" si="5"/>
@@ -8018,7 +8020,7 @@
       </c>
       <c r="AM7" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AN7" s="1">
         <f t="shared" si="7"/>
@@ -8190,11 +8192,11 @@
       </c>
       <c r="AJ8">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK8">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL8" s="1">
         <f t="shared" si="5"/>
@@ -8202,7 +8204,7 @@
       </c>
       <c r="AM8" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN8" s="1">
         <f t="shared" si="7"/>
@@ -8278,7 +8280,7 @@
       </c>
       <c r="F9" s="67" cm="1">
         <f t="array" ref="F9">_xlfn.XLOOKUP($D9&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
-        <v>0</v>
+        <v>27.02</v>
       </c>
       <c r="G9" s="67" cm="1">
         <f t="array" ref="G9">_xlfn.XLOOKUP($D9&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
@@ -8338,7 +8340,7 @@
       </c>
       <c r="AA9" s="2">
         <f t="shared" ca="1" si="22"/>
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AB9">
         <f t="shared" si="23"/>
@@ -8374,11 +8376,11 @@
       </c>
       <c r="AJ9">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AK9">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AL9" s="1">
         <f t="shared" si="5"/>
@@ -8386,7 +8388,7 @@
       </c>
       <c r="AM9" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AN9" s="1">
         <f t="shared" si="7"/>
@@ -8558,11 +8560,11 @@
       </c>
       <c r="AJ10">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK10">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL10" s="1">
         <f t="shared" si="5"/>
@@ -8570,7 +8572,7 @@
       </c>
       <c r="AM10" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN10" s="1">
         <f t="shared" si="7"/>
@@ -8742,11 +8744,11 @@
       </c>
       <c r="AJ11">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK11">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL11" s="1">
         <f t="shared" si="5"/>
@@ -8754,7 +8756,7 @@
       </c>
       <c r="AM11" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN11" s="1">
         <f t="shared" si="7"/>
@@ -8926,11 +8928,11 @@
       </c>
       <c r="AJ12">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK12">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL12" s="1">
         <f t="shared" si="5"/>
@@ -8938,7 +8940,7 @@
       </c>
       <c r="AM12" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN12" s="1">
         <f t="shared" si="7"/>
@@ -9110,11 +9112,11 @@
       </c>
       <c r="AJ13">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK13">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL13" s="1">
         <f t="shared" si="5"/>
@@ -9122,7 +9124,7 @@
       </c>
       <c r="AM13" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN13" s="1">
         <f t="shared" si="7"/>
@@ -9198,7 +9200,7 @@
       </c>
       <c r="F14" s="67" cm="1">
         <f t="array" ref="F14">_xlfn.XLOOKUP($D14&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
-        <v>0</v>
+        <v>33.869999999999997</v>
       </c>
       <c r="G14" s="67" cm="1">
         <f t="array" ref="G14">_xlfn.XLOOKUP($D14&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
@@ -9258,7 +9260,7 @@
       </c>
       <c r="AA14" s="2">
         <f t="shared" ca="1" si="22"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB14">
         <f t="shared" si="23"/>
@@ -9294,11 +9296,11 @@
       </c>
       <c r="AJ14">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK14">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL14" s="1">
         <f t="shared" si="5"/>
@@ -9306,7 +9308,7 @@
       </c>
       <c r="AM14" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN14" s="1">
         <f t="shared" si="7"/>
@@ -9478,11 +9480,11 @@
       </c>
       <c r="AJ15">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK15">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL15" s="1">
         <f t="shared" si="5"/>
@@ -9490,7 +9492,7 @@
       </c>
       <c r="AM15" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN15" s="1">
         <f t="shared" si="7"/>
@@ -9566,7 +9568,7 @@
       </c>
       <c r="F16" s="67" cm="1">
         <f t="array" ref="F16">_xlfn.XLOOKUP($D16&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
-        <v>0</v>
+        <v>30.39</v>
       </c>
       <c r="G16" s="67" cm="1">
         <f t="array" ref="G16">_xlfn.XLOOKUP($D16&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
@@ -9626,7 +9628,7 @@
       </c>
       <c r="AA16" s="2">
         <f t="shared" ca="1" si="22"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AB16">
         <f t="shared" si="23"/>
@@ -9662,11 +9664,11 @@
       </c>
       <c r="AJ16">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK16">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AL16" s="1">
         <f t="shared" si="5"/>
@@ -9674,7 +9676,7 @@
       </c>
       <c r="AM16" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AN16" s="1">
         <f t="shared" si="7"/>
@@ -9750,7 +9752,7 @@
       </c>
       <c r="F17" s="67" cm="1">
         <f t="array" ref="F17">_xlfn.XLOOKUP($D17&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
-        <v>0</v>
+        <v>25.22</v>
       </c>
       <c r="G17" s="67" cm="1">
         <f t="array" ref="G17">_xlfn.XLOOKUP($D17&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
@@ -9810,7 +9812,7 @@
       </c>
       <c r="AA17" s="2">
         <f t="shared" ca="1" si="22"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AB17">
         <f t="shared" si="23"/>
@@ -9846,11 +9848,11 @@
       </c>
       <c r="AJ17">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AK17">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AL17" s="1">
         <f t="shared" si="5"/>
@@ -9858,7 +9860,7 @@
       </c>
       <c r="AM17" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AN17" s="1">
         <f t="shared" si="7"/>
@@ -10030,11 +10032,11 @@
       </c>
       <c r="AJ18">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK18">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL18" s="1">
         <f t="shared" si="5"/>
@@ -10042,7 +10044,7 @@
       </c>
       <c r="AM18" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN18" s="1">
         <f t="shared" si="7"/>
@@ -10118,7 +10120,7 @@
       </c>
       <c r="F19" s="67" cm="1">
         <f t="array" ref="F19">_xlfn.XLOOKUP($D19&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
-        <v>0</v>
+        <v>31.32</v>
       </c>
       <c r="G19" s="67" cm="1">
         <f t="array" ref="G19">_xlfn.XLOOKUP($D19&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
@@ -10178,7 +10180,7 @@
       </c>
       <c r="AA19" s="2">
         <f t="shared" ca="1" si="22"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AB19">
         <f t="shared" si="23"/>
@@ -10214,11 +10216,11 @@
       </c>
       <c r="AJ19">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK19">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AL19" s="1">
         <f t="shared" si="5"/>
@@ -10226,7 +10228,7 @@
       </c>
       <c r="AM19" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN19" s="1">
         <f t="shared" si="7"/>
@@ -10398,11 +10400,11 @@
       </c>
       <c r="AJ20">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK20">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL20" s="1">
         <f t="shared" si="5"/>
@@ -10410,7 +10412,7 @@
       </c>
       <c r="AM20" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN20" s="1">
         <f t="shared" si="7"/>
@@ -10486,7 +10488,7 @@
       </c>
       <c r="F21" s="67" cm="1">
         <f t="array" ref="F21">_xlfn.XLOOKUP($D21&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
-        <v>0</v>
+        <v>24.02</v>
       </c>
       <c r="G21" s="67" cm="1">
         <f t="array" ref="G21">_xlfn.XLOOKUP($D21&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
@@ -10546,7 +10548,7 @@
       </c>
       <c r="AA21" s="2">
         <f t="shared" ca="1" si="22"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="AB21">
         <f t="shared" si="23"/>
@@ -10582,11 +10584,11 @@
       </c>
       <c r="AJ21">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AK21">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="AL21" s="1">
         <f t="shared" si="5"/>
@@ -10594,7 +10596,7 @@
       </c>
       <c r="AM21" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AN21" s="1">
         <f t="shared" si="7"/>
@@ -10766,11 +10768,11 @@
       </c>
       <c r="AJ22">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK22">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL22" s="1">
         <f t="shared" si="5"/>
@@ -10778,7 +10780,7 @@
       </c>
       <c r="AM22" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN22" s="1">
         <f t="shared" si="7"/>
@@ -10950,11 +10952,11 @@
       </c>
       <c r="AJ23">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK23">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL23" s="1">
         <f t="shared" si="5"/>
@@ -10962,7 +10964,7 @@
       </c>
       <c r="AM23" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN23" s="1">
         <f t="shared" si="7"/>
@@ -11134,11 +11136,11 @@
       </c>
       <c r="AJ24">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK24">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL24" s="1">
         <f t="shared" si="5"/>
@@ -11146,7 +11148,7 @@
       </c>
       <c r="AM24" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN24" s="1">
         <f t="shared" si="7"/>
@@ -11318,11 +11320,11 @@
       </c>
       <c r="AJ25">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK25">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL25" s="1">
         <f t="shared" si="5"/>
@@ -11330,7 +11332,7 @@
       </c>
       <c r="AM25" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN25" s="1">
         <f t="shared" si="7"/>
@@ -11406,7 +11408,7 @@
       </c>
       <c r="F26" s="67" cm="1">
         <f t="array" ref="F26">_xlfn.XLOOKUP($D26&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
-        <v>0</v>
+        <v>30.09</v>
       </c>
       <c r="G26" s="67" cm="1">
         <f t="array" ref="G26">_xlfn.XLOOKUP($D26&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
@@ -11466,7 +11468,7 @@
       </c>
       <c r="AA26" s="2">
         <f t="shared" ca="1" si="22"/>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AB26">
         <f t="shared" si="23"/>
@@ -11502,11 +11504,11 @@
       </c>
       <c r="AJ26">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AK26">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AL26" s="1">
         <f t="shared" si="5"/>
@@ -11514,7 +11516,7 @@
       </c>
       <c r="AM26" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AN26" s="1">
         <f t="shared" si="7"/>
@@ -11686,11 +11688,11 @@
       </c>
       <c r="AJ27">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK27">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL27" s="1">
         <f t="shared" si="5"/>
@@ -11698,7 +11700,7 @@
       </c>
       <c r="AM27" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN27" s="1">
         <f t="shared" si="7"/>
@@ -11774,7 +11776,7 @@
       </c>
       <c r="F28" s="67" cm="1">
         <f t="array" ref="F28">_xlfn.XLOOKUP($D28&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
-        <v>0</v>
+        <v>30.01</v>
       </c>
       <c r="G28" s="67" cm="1">
         <f t="array" ref="G28">_xlfn.XLOOKUP($D28&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
@@ -11834,7 +11836,7 @@
       </c>
       <c r="AA28" s="2">
         <f t="shared" ca="1" si="22"/>
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AB28">
         <f t="shared" ref="AB28:AJ28" si="30">AC28-LARGE($AL28:$AZ28,AB$3)</f>
@@ -11870,11 +11872,11 @@
       </c>
       <c r="AJ28">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AK28">
         <f>SUM(AL28:AZ28)</f>
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AL28" s="1">
         <f t="shared" si="5"/>
@@ -11882,7 +11884,7 @@
       </c>
       <c r="AM28" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AN28" s="1">
         <f t="shared" si="7"/>
@@ -12054,11 +12056,11 @@
       </c>
       <c r="AJ29">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK29">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL29" s="1">
         <f t="shared" si="5"/>
@@ -12066,7 +12068,7 @@
       </c>
       <c r="AM29" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN29" s="1">
         <f t="shared" si="7"/>
@@ -12142,7 +12144,7 @@
       </c>
       <c r="F30" s="67" cm="1">
         <f t="array" ref="F30">_xlfn.XLOOKUP($D30&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="G30" s="67" cm="1">
         <f t="array" ref="G30">_xlfn.XLOOKUP($D30&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
@@ -12202,7 +12204,7 @@
       </c>
       <c r="AA30" s="2">
         <f t="shared" ca="1" si="22"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AB30">
         <f t="shared" si="23"/>
@@ -12238,11 +12240,11 @@
       </c>
       <c r="AJ30">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK30">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AL30" s="1">
         <f t="shared" si="5"/>
@@ -12250,7 +12252,7 @@
       </c>
       <c r="AM30" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN30" s="1">
         <f t="shared" si="7"/>
@@ -12326,7 +12328,7 @@
       </c>
       <c r="F31" s="67" cm="1">
         <f t="array" ref="F31">_xlfn.XLOOKUP($D31&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
-        <v>0</v>
+        <v>30.96</v>
       </c>
       <c r="G31" s="67" cm="1">
         <f t="array" ref="G31">_xlfn.XLOOKUP($D31&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
@@ -12386,7 +12388,7 @@
       </c>
       <c r="AA31" s="2">
         <f t="shared" ca="1" si="22"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AB31">
         <f t="shared" si="23"/>
@@ -12422,11 +12424,11 @@
       </c>
       <c r="AJ31">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AK31">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AL31" s="1">
         <f t="shared" si="5"/>
@@ -12434,7 +12436,7 @@
       </c>
       <c r="AM31" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN31" s="1">
         <f t="shared" si="7"/>
@@ -12606,11 +12608,11 @@
       </c>
       <c r="AJ32">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK32">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL32" s="1">
         <f t="shared" si="5"/>
@@ -12618,7 +12620,7 @@
       </c>
       <c r="AM32" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN32" s="1">
         <f t="shared" si="7"/>
@@ -12694,7 +12696,7 @@
       </c>
       <c r="F33" s="67" cm="1">
         <f t="array" ref="F33">_xlfn.XLOOKUP($D33&amp;F$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
-        <v>0</v>
+        <v>32.44</v>
       </c>
       <c r="G33" s="67" cm="1">
         <f t="array" ref="G33">_xlfn.XLOOKUP($D33&amp;G$1,DayRankSpeed!$C:$C&amp;DayRankSpeed!$B:$B,DayRankSpeed!$D:$D,0,0)</f>
@@ -12754,7 +12756,7 @@
       </c>
       <c r="AA33" s="2">
         <f t="shared" ca="1" si="22"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AB33">
         <f t="shared" si="23"/>
@@ -12790,11 +12792,11 @@
       </c>
       <c r="AJ33">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK33">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AL33" s="1">
         <f t="shared" si="5"/>
@@ -12802,7 +12804,7 @@
       </c>
       <c r="AM33" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN33" s="1">
         <f t="shared" si="7"/>
@@ -12974,11 +12976,11 @@
       </c>
       <c r="AJ34">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK34">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL34" s="1">
         <f t="shared" si="5"/>
@@ -12986,7 +12988,7 @@
       </c>
       <c r="AM34" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN34" s="1">
         <f t="shared" si="7"/>
@@ -13158,11 +13160,11 @@
       </c>
       <c r="AJ35">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK35">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL35" s="1">
         <f t="shared" si="5"/>
@@ -13170,7 +13172,7 @@
       </c>
       <c r="AM35" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN35" s="1">
         <f t="shared" si="7"/>
@@ -13342,11 +13344,11 @@
       </c>
       <c r="AJ36">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK36">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AL36" s="1">
         <f t="shared" si="5"/>
@@ -13354,7 +13356,7 @@
       </c>
       <c r="AM36" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN36" s="1">
         <f t="shared" si="7"/>
@@ -14083,7 +14085,7 @@
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
 </worksheet>
 </file>
 
